--- a/upload_excel/Redirection_Test.xlsx
+++ b/upload_excel/Redirection_Test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CNXK\Downloads\tagging\unpacktoolgit\upload_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyuns\Downloads\unpacktool\unpacktool\upload_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B5A962-BB01-4047-899A-127D23B2EA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DCF409-1BB2-4483-A532-9A03D5817EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30195" yWindow="1395" windowWidth="21600" windowHeight="11295" tabRatio="877" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39675" yWindow="8070" windowWidth="29385" windowHeight="10740" tabRatio="877" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20210728 AA (KV)" sheetId="73" state="hidden" r:id="rId1"/>
@@ -5837,22 +5837,22 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J97"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" style="2" customWidth="1"/>
-    <col min="3" max="5" width="15.6640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.44140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="80.6640625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="80.6640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="53.88671875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="15.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="80.7109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="80.7109375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="53.85546875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J1"/>
     </row>
-    <row r="2" spans="1:10" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
@@ -5865,7 +5865,7 @@
       <c r="I2" s="4"/>
       <c r="J2"/>
     </row>
-    <row r="3" spans="1:10" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -5873,7 +5873,7 @@
       <c r="F3" s="25"/>
       <c r="H3" s="25"/>
     </row>
-    <row r="4" spans="1:10" s="7" customFormat="1" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
         <v>1</v>
@@ -5885,7 +5885,7 @@
       <c r="G4" s="6"/>
       <c r="H4" s="33"/>
     </row>
-    <row r="5" spans="1:10" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="1" t="s">
         <v>2</v>
@@ -5897,7 +5897,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="25"/>
     </row>
-    <row r="6" spans="1:10" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="1" t="s">
         <v>3</v>
@@ -5909,7 +5909,7 @@
       <c r="G6" s="1"/>
       <c r="H6" s="25"/>
     </row>
-    <row r="7" spans="1:10" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="32" t="s">
         <v>4</v>
@@ -5921,7 +5921,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="19"/>
     </row>
-    <row r="8" spans="1:10" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -5929,7 +5929,7 @@
       <c r="F8" s="25"/>
       <c r="H8" s="25"/>
     </row>
-    <row r="9" spans="1:10" s="7" customFormat="1" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="18"/>
       <c r="C9" s="6"/>
@@ -5945,7 +5945,7 @@
       <c r="I9" s="92"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="s">
         <v>7</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>14</v>
       </c>
@@ -5997,7 +5997,7 @@
       <c r="I11" s="22"/>
       <c r="J11" s="22"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
         <v>14</v>
       </c>
@@ -6020,7 +6020,7 @@
       <c r="I12" s="13"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>14</v>
       </c>
@@ -6043,7 +6043,7 @@
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>14</v>
       </c>
@@ -6066,7 +6066,7 @@
       <c r="I14" s="12"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>14</v>
       </c>
@@ -6089,7 +6089,7 @@
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>14</v>
       </c>
@@ -6112,7 +6112,7 @@
       <c r="I16" s="13"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>14</v>
       </c>
@@ -6135,7 +6135,7 @@
       <c r="I17" s="13"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>14</v>
       </c>
@@ -6158,7 +6158,7 @@
       <c r="I18" s="13"/>
       <c r="J18" s="12"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>14</v>
       </c>
@@ -6181,7 +6181,7 @@
       <c r="I19" s="13"/>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>14</v>
       </c>
@@ -6204,7 +6204,7 @@
       <c r="I20" s="13"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>14</v>
       </c>
@@ -6227,7 +6227,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>14</v>
       </c>
@@ -6250,7 +6250,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>14</v>
       </c>
@@ -6273,7 +6273,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>14</v>
       </c>
@@ -6296,7 +6296,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="14" t="s">
         <v>14</v>
       </c>
@@ -6313,7 +6313,7 @@
       <c r="I25" s="13"/>
       <c r="J25" s="12"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>14</v>
       </c>
@@ -6330,7 +6330,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>14</v>
       </c>
@@ -6347,7 +6347,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>14</v>
       </c>
@@ -6364,7 +6364,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>14</v>
       </c>
@@ -6381,7 +6381,7 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>14</v>
       </c>
@@ -6398,7 +6398,7 @@
       <c r="I30" s="13"/>
       <c r="J30" s="12"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>14</v>
       </c>
@@ -6415,7 +6415,7 @@
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>14</v>
       </c>
@@ -6432,7 +6432,7 @@
       <c r="I32" s="13"/>
       <c r="J32" s="12"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>14</v>
       </c>
@@ -6449,7 +6449,7 @@
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>14</v>
       </c>
@@ -6466,7 +6466,7 @@
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>14</v>
       </c>
@@ -6483,7 +6483,7 @@
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>14</v>
       </c>
@@ -6500,7 +6500,7 @@
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>14</v>
       </c>
@@ -6517,7 +6517,7 @@
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>14</v>
       </c>
@@ -6534,7 +6534,7 @@
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>14</v>
       </c>
@@ -6551,7 +6551,7 @@
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>14</v>
       </c>
@@ -6574,7 +6574,7 @@
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>14</v>
       </c>
@@ -6597,7 +6597,7 @@
       <c r="I41" s="12"/>
       <c r="J41" s="12"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="9" t="s">
         <v>14</v>
       </c>
@@ -6620,7 +6620,7 @@
       <c r="I42" s="12"/>
       <c r="J42" s="12"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="9" t="s">
         <v>14</v>
       </c>
@@ -6643,7 +6643,7 @@
       <c r="I43" s="12"/>
       <c r="J43" s="12"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="9" t="s">
         <v>14</v>
       </c>
@@ -6666,7 +6666,7 @@
       <c r="I44" s="13"/>
       <c r="J44" s="12"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="9" t="s">
         <v>14</v>
       </c>
@@ -6689,7 +6689,7 @@
       <c r="I45" s="12"/>
       <c r="J45" s="12"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="9" t="s">
         <v>14</v>
       </c>
@@ -6712,7 +6712,7 @@
       <c r="I46" s="28"/>
       <c r="J46" s="12"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="9" t="s">
         <v>14</v>
       </c>
@@ -6735,7 +6735,7 @@
       <c r="I47" s="12"/>
       <c r="J47" s="12"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="9" t="s">
         <v>61</v>
       </c>
@@ -6758,7 +6758,7 @@
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="9" t="s">
         <v>14</v>
       </c>
@@ -6781,7 +6781,7 @@
       <c r="I49" s="12"/>
       <c r="J49" s="12"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="9" t="s">
         <v>14</v>
       </c>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="J50" s="12"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="9" t="s">
         <v>14</v>
       </c>
@@ -6831,7 +6831,7 @@
       <c r="I51" s="12"/>
       <c r="J51" s="12"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="9" t="s">
         <v>14</v>
       </c>
@@ -6854,7 +6854,7 @@
       <c r="I52" s="12"/>
       <c r="J52" s="12"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="9" t="s">
         <v>14</v>
       </c>
@@ -6877,7 +6877,7 @@
       <c r="I53" s="12"/>
       <c r="J53" s="12"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="9" t="s">
         <v>14</v>
       </c>
@@ -6900,7 +6900,7 @@
       <c r="I54" s="12"/>
       <c r="J54" s="12"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="9" t="s">
         <v>14</v>
       </c>
@@ -6923,7 +6923,7 @@
       <c r="I55" s="12"/>
       <c r="J55" s="12"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="9" t="s">
         <v>14</v>
       </c>
@@ -6946,7 +6946,7 @@
       <c r="I56" s="12"/>
       <c r="J56" s="12"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="9" t="s">
         <v>14</v>
       </c>
@@ -6969,7 +6969,7 @@
       <c r="I57" s="12"/>
       <c r="J57" s="12"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="9" t="s">
         <v>14</v>
       </c>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="J58" s="12"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="9" t="s">
         <v>14</v>
       </c>
@@ -7019,7 +7019,7 @@
       <c r="I59" s="12"/>
       <c r="J59" s="12"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="9" t="s">
         <v>14</v>
       </c>
@@ -7042,7 +7042,7 @@
       <c r="I60" s="12"/>
       <c r="J60" s="12"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="9" t="s">
         <v>61</v>
       </c>
@@ -7065,7 +7065,7 @@
       <c r="I61" s="12"/>
       <c r="J61" s="12"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="9" t="s">
         <v>61</v>
       </c>
@@ -7088,7 +7088,7 @@
       <c r="I62" s="12"/>
       <c r="J62" s="12"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="9" t="s">
         <v>14</v>
       </c>
@@ -7111,7 +7111,7 @@
       <c r="I63" s="12"/>
       <c r="J63" s="12"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="9" t="s">
         <v>14</v>
       </c>
@@ -7134,7 +7134,7 @@
       <c r="I64" s="12"/>
       <c r="J64" s="12"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="9" t="s">
         <v>88</v>
       </c>
@@ -7157,7 +7157,7 @@
       <c r="I65" s="12"/>
       <c r="J65" s="12"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="9" t="s">
         <v>88</v>
       </c>
@@ -7180,7 +7180,7 @@
       <c r="I66" s="12"/>
       <c r="J66" s="12"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="9" t="s">
         <v>91</v>
       </c>
@@ -7203,7 +7203,7 @@
       <c r="I67" s="12"/>
       <c r="J67" s="12"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="9" t="s">
         <v>88</v>
       </c>
@@ -7226,7 +7226,7 @@
       <c r="I68" s="12"/>
       <c r="J68" s="12"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="9" t="s">
         <v>88</v>
       </c>
@@ -7249,7 +7249,7 @@
       <c r="I69" s="12"/>
       <c r="J69" s="12"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="9" t="s">
         <v>88</v>
       </c>
@@ -7272,7 +7272,7 @@
       <c r="I70" s="12"/>
       <c r="J70" s="12"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="9" t="s">
         <v>88</v>
       </c>
@@ -7295,7 +7295,7 @@
       <c r="I71" s="12"/>
       <c r="J71" s="12"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="9" t="s">
         <v>88</v>
       </c>
@@ -7318,7 +7318,7 @@
       <c r="I72" s="12"/>
       <c r="J72" s="12"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="9" t="s">
         <v>88</v>
       </c>
@@ -7341,7 +7341,7 @@
       <c r="I73" s="12"/>
       <c r="J73" s="12"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="9" t="s">
         <v>88</v>
       </c>
@@ -7364,7 +7364,7 @@
       <c r="I74" s="12"/>
       <c r="J74" s="12"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="9" t="s">
         <v>88</v>
       </c>
@@ -7387,7 +7387,7 @@
       <c r="I75" s="12"/>
       <c r="J75" s="12"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="9" t="s">
         <v>88</v>
       </c>
@@ -7410,7 +7410,7 @@
       <c r="I76" s="12"/>
       <c r="J76" s="12"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="9" t="s">
         <v>88</v>
       </c>
@@ -7433,7 +7433,7 @@
       <c r="I77" s="12"/>
       <c r="J77" s="12"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="9" t="s">
         <v>88</v>
       </c>
@@ -7456,7 +7456,7 @@
       <c r="I78" s="12"/>
       <c r="J78" s="12"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="9" t="s">
         <v>88</v>
       </c>
@@ -7479,7 +7479,7 @@
       <c r="I79" s="12"/>
       <c r="J79" s="12"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="9" t="s">
         <v>88</v>
       </c>
@@ -7502,7 +7502,7 @@
       <c r="I80" s="12"/>
       <c r="J80" s="12"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="9" t="s">
         <v>88</v>
       </c>
@@ -7525,7 +7525,7 @@
       <c r="I81" s="12"/>
       <c r="J81" s="12"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="9" t="s">
         <v>88</v>
       </c>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="J82" s="12"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="9" t="s">
         <v>88</v>
       </c>
@@ -7575,7 +7575,7 @@
       <c r="I83" s="12"/>
       <c r="J83" s="12"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="9" t="s">
         <v>88</v>
       </c>
@@ -7598,7 +7598,7 @@
       <c r="I84" s="12"/>
       <c r="J84" s="12"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="9" t="s">
         <v>88</v>
       </c>
@@ -7621,7 +7621,7 @@
       <c r="I85" s="12"/>
       <c r="J85" s="12"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="9" t="s">
         <v>88</v>
       </c>
@@ -7644,7 +7644,7 @@
       <c r="I86" s="12"/>
       <c r="J86" s="12"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="9" t="s">
         <v>91</v>
       </c>
@@ -7667,7 +7667,7 @@
       <c r="I87" s="12"/>
       <c r="J87" s="12"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="9" t="s">
         <v>88</v>
       </c>
@@ -7690,7 +7690,7 @@
       <c r="I88" s="12"/>
       <c r="J88" s="12"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="9" t="s">
         <v>88</v>
       </c>
@@ -7713,7 +7713,7 @@
       <c r="I89" s="12"/>
       <c r="J89" s="12"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="9" t="s">
         <v>88</v>
       </c>
@@ -7736,7 +7736,7 @@
       <c r="I90" s="12"/>
       <c r="J90" s="12"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="9" t="s">
         <v>88</v>
       </c>
@@ -7759,7 +7759,7 @@
       <c r="I91" s="12"/>
       <c r="J91" s="12"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="49" t="s">
         <v>88</v>
       </c>
@@ -7782,7 +7782,7 @@
       <c r="I92" s="12"/>
       <c r="J92" s="31"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="49" t="s">
         <v>88</v>
       </c>
@@ -7805,7 +7805,7 @@
       <c r="I93" s="12"/>
       <c r="J93" s="31"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="49" t="s">
         <v>88</v>
       </c>
@@ -7828,7 +7828,7 @@
       <c r="I94" s="12"/>
       <c r="J94" s="31"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="9" t="s">
         <v>88</v>
       </c>
@@ -7851,7 +7851,7 @@
       <c r="I95" s="12"/>
       <c r="J95" s="12"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="49" t="s">
         <v>88</v>
       </c>
@@ -7874,7 +7874,7 @@
       <c r="I96" s="12"/>
       <c r="J96" s="31"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="52" t="s">
         <v>88</v>
       </c>
@@ -7916,26 +7916,26 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:L98"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" style="2" customWidth="1"/>
-    <col min="3" max="5" width="15.6640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="25.6640625" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" customWidth="1"/>
-    <col min="8" max="8" width="70.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.6640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="20.6640625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="70.6640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="15.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="70.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="70.7109375" style="3" customWidth="1"/>
     <col min="12" max="12" width="49" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="L1"/>
     </row>
-    <row r="2" spans="1:12" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
         <v>127</v>
       </c>
@@ -7950,7 +7950,7 @@
       <c r="K2" s="4"/>
       <c r="L2"/>
     </row>
-    <row r="3" spans="1:12" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -7960,7 +7960,7 @@
       <c r="I3" s="25"/>
       <c r="J3" s="25"/>
     </row>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
         <v>1</v>
@@ -7974,7 +7974,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:12" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="1" t="s">
         <v>128</v>
@@ -7988,7 +7988,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:12" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="1" t="s">
         <v>129</v>
@@ -8002,7 +8002,7 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:12" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="1" t="s">
         <v>130</v>
@@ -8016,7 +8016,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:12" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="1" t="s">
         <v>131</v>
@@ -8030,7 +8030,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="19"/>
     </row>
-    <row r="9" spans="1:12" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="32" t="s">
         <v>4</v>
@@ -8044,7 +8044,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="19"/>
     </row>
-    <row r="10" spans="1:12" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -8054,7 +8054,7 @@
       <c r="I10" s="25"/>
       <c r="J10" s="25"/>
     </row>
-    <row r="11" spans="1:12" s="7" customFormat="1" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="18"/>
       <c r="C11" s="6"/>
@@ -8072,7 +8072,7 @@
       <c r="K11" s="92"/>
       <c r="L11" s="6"/>
     </row>
-    <row r="12" spans="1:12" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
         <v>7</v>
       </c>
@@ -8107,7 +8107,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>14</v>
       </c>
@@ -8126,7 +8126,7 @@
       <c r="K13" s="22"/>
       <c r="L13" s="22"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>14</v>
       </c>
@@ -8145,7 +8145,7 @@
       <c r="K14" s="13"/>
       <c r="L14" s="12"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>14</v>
       </c>
@@ -8164,7 +8164,7 @@
       <c r="K15" s="12"/>
       <c r="L15" s="12"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>14</v>
       </c>
@@ -8183,7 +8183,7 @@
       <c r="K16" s="12"/>
       <c r="L16" s="30"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>14</v>
       </c>
@@ -8202,7 +8202,7 @@
       <c r="K17" s="12"/>
       <c r="L17" s="12"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>14</v>
       </c>
@@ -8221,7 +8221,7 @@
       <c r="K18" s="13"/>
       <c r="L18" s="12"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>14</v>
       </c>
@@ -8240,7 +8240,7 @@
       <c r="K19" s="13"/>
       <c r="L19" s="12"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>14</v>
       </c>
@@ -8259,7 +8259,7 @@
       <c r="K20" s="13"/>
       <c r="L20" s="12"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>14</v>
       </c>
@@ -8278,7 +8278,7 @@
       <c r="K21" s="13"/>
       <c r="L21" s="12"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>14</v>
       </c>
@@ -8297,7 +8297,7 @@
       <c r="K22" s="12"/>
       <c r="L22" s="30"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>14</v>
       </c>
@@ -8316,7 +8316,7 @@
       <c r="K23" s="12"/>
       <c r="L23" s="12"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>14</v>
       </c>
@@ -8335,7 +8335,7 @@
       <c r="K24" s="12"/>
       <c r="L24" s="12"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>14</v>
       </c>
@@ -8354,7 +8354,7 @@
       <c r="K25" s="12"/>
       <c r="L25" s="30"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="14" t="s">
         <v>14</v>
       </c>
@@ -8373,7 +8373,7 @@
       <c r="K26" s="13"/>
       <c r="L26" s="12"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>14</v>
       </c>
@@ -8392,7 +8392,7 @@
       <c r="K27" s="12"/>
       <c r="L27" s="12"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>14</v>
       </c>
@@ -8411,7 +8411,7 @@
       <c r="K28" s="12"/>
       <c r="L28" s="12"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>14</v>
       </c>
@@ -8430,7 +8430,7 @@
       <c r="K29" s="12"/>
       <c r="L29" s="12"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>14</v>
       </c>
@@ -8449,7 +8449,7 @@
       <c r="K30" s="12"/>
       <c r="L30" s="12"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>14</v>
       </c>
@@ -8468,7 +8468,7 @@
       <c r="K31" s="13"/>
       <c r="L31" s="12"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>14</v>
       </c>
@@ -8487,7 +8487,7 @@
       <c r="K32" s="12"/>
       <c r="L32" s="12"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>14</v>
       </c>
@@ -8506,7 +8506,7 @@
       <c r="K33" s="13"/>
       <c r="L33" s="12"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>14</v>
       </c>
@@ -8525,7 +8525,7 @@
       <c r="K34" s="12"/>
       <c r="L34" s="12"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>14</v>
       </c>
@@ -8544,7 +8544,7 @@
       <c r="K35" s="12"/>
       <c r="L35" s="12"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>14</v>
       </c>
@@ -8563,7 +8563,7 @@
       <c r="K36" s="12"/>
       <c r="L36" s="12"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>14</v>
       </c>
@@ -8582,7 +8582,7 @@
       <c r="K37" s="12"/>
       <c r="L37" s="12"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>14</v>
       </c>
@@ -8601,7 +8601,7 @@
       <c r="K38" s="12"/>
       <c r="L38" s="12"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>14</v>
       </c>
@@ -8620,7 +8620,7 @@
       <c r="K39" s="12"/>
       <c r="L39" s="12"/>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>14</v>
       </c>
@@ -8639,7 +8639,7 @@
       <c r="K40" s="12"/>
       <c r="L40" s="12"/>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>14</v>
       </c>
@@ -8666,7 +8666,7 @@
       <c r="K41" s="12"/>
       <c r="L41" s="12"/>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B42" s="9" t="s">
         <v>14</v>
       </c>
@@ -8693,7 +8693,7 @@
       <c r="K42" s="12"/>
       <c r="L42" s="12"/>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" s="9" t="s">
         <v>14</v>
       </c>
@@ -8720,7 +8720,7 @@
       <c r="K43" s="12"/>
       <c r="L43" s="12"/>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B44" s="9" t="s">
         <v>14</v>
       </c>
@@ -8747,7 +8747,7 @@
       <c r="K44" s="12"/>
       <c r="L44" s="12"/>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B45" s="9" t="s">
         <v>14</v>
       </c>
@@ -8774,7 +8774,7 @@
       <c r="K45" s="13"/>
       <c r="L45" s="12"/>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B46" s="9" t="s">
         <v>14</v>
       </c>
@@ -8801,7 +8801,7 @@
       <c r="K46" s="12"/>
       <c r="L46" s="12"/>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="9" t="s">
         <v>14</v>
       </c>
@@ -8828,7 +8828,7 @@
       <c r="K47" s="28"/>
       <c r="L47" s="12"/>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="9" t="s">
         <v>14</v>
       </c>
@@ -8855,7 +8855,7 @@
       <c r="K48" s="12"/>
       <c r="L48" s="12"/>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" s="9" t="s">
         <v>61</v>
       </c>
@@ -8882,7 +8882,7 @@
       <c r="K49" s="12"/>
       <c r="L49" s="12"/>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="9" t="s">
         <v>14</v>
       </c>
@@ -8909,7 +8909,7 @@
       <c r="K50" s="12"/>
       <c r="L50" s="12"/>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" s="9" t="s">
         <v>14</v>
       </c>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="L51" s="12"/>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="9" t="s">
         <v>14</v>
       </c>
@@ -8969,7 +8969,7 @@
       <c r="K52" s="12"/>
       <c r="L52" s="12"/>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" s="9" t="s">
         <v>14</v>
       </c>
@@ -8996,7 +8996,7 @@
       <c r="K53" s="12"/>
       <c r="L53" s="12"/>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" s="9" t="s">
         <v>14</v>
       </c>
@@ -9023,7 +9023,7 @@
       <c r="K54" s="12"/>
       <c r="L54" s="12"/>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B55" s="9" t="s">
         <v>14</v>
       </c>
@@ -9050,7 +9050,7 @@
       <c r="K55" s="12"/>
       <c r="L55" s="12"/>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B56" s="9" t="s">
         <v>14</v>
       </c>
@@ -9077,7 +9077,7 @@
       <c r="K56" s="12"/>
       <c r="L56" s="12"/>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B57" s="9" t="s">
         <v>14</v>
       </c>
@@ -9104,7 +9104,7 @@
       <c r="K57" s="12"/>
       <c r="L57" s="12"/>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B58" s="9" t="s">
         <v>14</v>
       </c>
@@ -9131,7 +9131,7 @@
       <c r="K58" s="12"/>
       <c r="L58" s="12"/>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B59" s="9" t="s">
         <v>14</v>
       </c>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="L59" s="12"/>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B60" s="9" t="s">
         <v>14</v>
       </c>
@@ -9191,7 +9191,7 @@
       <c r="K60" s="12"/>
       <c r="L60" s="12"/>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B61" s="9" t="s">
         <v>14</v>
       </c>
@@ -9218,7 +9218,7 @@
       <c r="K61" s="12"/>
       <c r="L61" s="12"/>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B62" s="9" t="s">
         <v>61</v>
       </c>
@@ -9245,7 +9245,7 @@
       <c r="K62" s="12"/>
       <c r="L62" s="12"/>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B63" s="9" t="s">
         <v>61</v>
       </c>
@@ -9272,7 +9272,7 @@
       <c r="K63" s="12"/>
       <c r="L63" s="12"/>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B64" s="9" t="s">
         <v>14</v>
       </c>
@@ -9299,7 +9299,7 @@
       <c r="K64" s="12"/>
       <c r="L64" s="12"/>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B65" s="9" t="s">
         <v>14</v>
       </c>
@@ -9326,7 +9326,7 @@
       <c r="K65" s="12"/>
       <c r="L65" s="12"/>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B66" s="9" t="s">
         <v>88</v>
       </c>
@@ -9353,7 +9353,7 @@
       <c r="K66" s="12"/>
       <c r="L66" s="12"/>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B67" s="9" t="s">
         <v>88</v>
       </c>
@@ -9380,7 +9380,7 @@
       <c r="K67" s="12"/>
       <c r="L67" s="12"/>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B68" s="9" t="s">
         <v>91</v>
       </c>
@@ -9407,7 +9407,7 @@
       <c r="K68" s="12"/>
       <c r="L68" s="12"/>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B69" s="9" t="s">
         <v>88</v>
       </c>
@@ -9434,7 +9434,7 @@
       <c r="K69" s="12"/>
       <c r="L69" s="12"/>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B70" s="9" t="s">
         <v>88</v>
       </c>
@@ -9461,7 +9461,7 @@
       <c r="K70" s="12"/>
       <c r="L70" s="12"/>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B71" s="9" t="s">
         <v>88</v>
       </c>
@@ -9488,7 +9488,7 @@
       <c r="K71" s="12"/>
       <c r="L71" s="12"/>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B72" s="9" t="s">
         <v>88</v>
       </c>
@@ -9515,7 +9515,7 @@
       <c r="K72" s="12"/>
       <c r="L72" s="12"/>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B73" s="9" t="s">
         <v>88</v>
       </c>
@@ -9542,7 +9542,7 @@
       <c r="K73" s="12"/>
       <c r="L73" s="12"/>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B74" s="9" t="s">
         <v>88</v>
       </c>
@@ -9569,7 +9569,7 @@
       <c r="K74" s="12"/>
       <c r="L74" s="12"/>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B75" s="9" t="s">
         <v>88</v>
       </c>
@@ -9596,7 +9596,7 @@
       <c r="K75" s="12"/>
       <c r="L75" s="12"/>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B76" s="9" t="s">
         <v>88</v>
       </c>
@@ -9623,7 +9623,7 @@
       <c r="K76" s="12"/>
       <c r="L76" s="12"/>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B77" s="9" t="s">
         <v>88</v>
       </c>
@@ -9650,7 +9650,7 @@
       <c r="K77" s="12"/>
       <c r="L77" s="12"/>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B78" s="9" t="s">
         <v>88</v>
       </c>
@@ -9677,7 +9677,7 @@
       <c r="K78" s="12"/>
       <c r="L78" s="12"/>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B79" s="9" t="s">
         <v>88</v>
       </c>
@@ -9704,7 +9704,7 @@
       <c r="K79" s="12"/>
       <c r="L79" s="12"/>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B80" s="9" t="s">
         <v>88</v>
       </c>
@@ -9727,7 +9727,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B81" s="9" t="s">
         <v>88</v>
       </c>
@@ -9754,7 +9754,7 @@
       <c r="K81" s="12"/>
       <c r="L81" s="12"/>
     </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B82" s="9" t="s">
         <v>88</v>
       </c>
@@ -9781,7 +9781,7 @@
       <c r="K82" s="12"/>
       <c r="L82" s="12"/>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B83" s="9" t="s">
         <v>88</v>
       </c>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="L83" s="12"/>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B84" s="9" t="s">
         <v>88</v>
       </c>
@@ -9841,7 +9841,7 @@
       <c r="K84" s="12"/>
       <c r="L84" s="12"/>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B85" s="9" t="s">
         <v>88</v>
       </c>
@@ -9868,7 +9868,7 @@
       <c r="K85" s="12"/>
       <c r="L85" s="12"/>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B86" s="9" t="s">
         <v>88</v>
       </c>
@@ -9895,7 +9895,7 @@
       <c r="K86" s="12"/>
       <c r="L86" s="12"/>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B87" s="9" t="s">
         <v>88</v>
       </c>
@@ -9922,7 +9922,7 @@
       <c r="K87" s="12"/>
       <c r="L87" s="12"/>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B88" s="9" t="s">
         <v>91</v>
       </c>
@@ -9949,7 +9949,7 @@
       <c r="K88" s="12"/>
       <c r="L88" s="12"/>
     </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B89" s="9" t="s">
         <v>88</v>
       </c>
@@ -9976,7 +9976,7 @@
       <c r="K89" s="12"/>
       <c r="L89" s="12"/>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B90" s="9" t="s">
         <v>88</v>
       </c>
@@ -10003,7 +10003,7 @@
       <c r="K90" s="12"/>
       <c r="L90" s="12"/>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B91" s="9" t="s">
         <v>88</v>
       </c>
@@ -10030,7 +10030,7 @@
       <c r="K91" s="12"/>
       <c r="L91" s="12"/>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B92" s="9" t="s">
         <v>88</v>
       </c>
@@ -10057,7 +10057,7 @@
       <c r="K92" s="12"/>
       <c r="L92" s="12"/>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B93" s="49" t="s">
         <v>88</v>
       </c>
@@ -10084,7 +10084,7 @@
       <c r="K93" s="12"/>
       <c r="L93" s="31"/>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B94" s="49" t="s">
         <v>88</v>
       </c>
@@ -10111,7 +10111,7 @@
       <c r="K94" s="12"/>
       <c r="L94" s="31"/>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B95" s="49" t="s">
         <v>88</v>
       </c>
@@ -10138,7 +10138,7 @@
       <c r="K95" s="12"/>
       <c r="L95" s="31"/>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B96" s="9" t="s">
         <v>88</v>
       </c>
@@ -10165,7 +10165,7 @@
       <c r="K96" s="12"/>
       <c r="L96" s="12"/>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B97" s="49" t="s">
         <v>88</v>
       </c>
@@ -10192,7 +10192,7 @@
       <c r="K97" s="12"/>
       <c r="L97" s="31"/>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B98" s="52" t="s">
         <v>88</v>
       </c>
@@ -10238,26 +10238,26 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="B1:M169"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="40" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" style="2" customWidth="1"/>
-    <col min="3" max="5" width="15.6640625" style="41" customWidth="1"/>
-    <col min="6" max="6" width="48.109375" style="40" customWidth="1"/>
-    <col min="7" max="7" width="45.6640625" style="42" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="41" customWidth="1"/>
-    <col min="9" max="9" width="53.44140625" style="41" customWidth="1"/>
-    <col min="10" max="10" width="18.44140625" style="41" customWidth="1"/>
-    <col min="11" max="11" width="57.44140625" style="41" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.109375" style="41" customWidth="1"/>
-    <col min="13" max="13" width="85.33203125" style="41" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="40"/>
+    <col min="1" max="1" width="3.7109375" style="40" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="15.7109375" style="41" customWidth="1"/>
+    <col min="6" max="6" width="48.140625" style="40" customWidth="1"/>
+    <col min="7" max="7" width="45.7109375" style="42" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" style="41" customWidth="1"/>
+    <col min="9" max="9" width="53.42578125" style="41" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" style="41" customWidth="1"/>
+    <col min="11" max="11" width="57.42578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.140625" style="41" customWidth="1"/>
+    <col min="13" max="13" width="85.28515625" style="41" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.25">
       <c r="M1" s="40"/>
     </row>
-    <row r="2" spans="2:13" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:13" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
         <v>140</v>
       </c>
@@ -10273,7 +10273,7 @@
       <c r="L2" s="4"/>
       <c r="M2" s="40"/>
     </row>
-    <row r="3" spans="2:13" s="7" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:13" s="7" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -10283,7 +10283,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="25"/>
     </row>
-    <row r="4" spans="2:13" s="7" customFormat="1" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:13" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>141</v>
       </c>
@@ -10299,7 +10299,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="19"/>
     </row>
-    <row r="5" spans="2:13" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:13" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>143</v>
       </c>
@@ -10315,7 +10315,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="19"/>
     </row>
-    <row r="6" spans="2:13" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:13" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="B6" s="32" t="s">
         <v>4</v>
       </c>
@@ -10331,7 +10331,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="19"/>
     </row>
-    <row r="7" spans="2:13" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:13" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -10341,7 +10341,7 @@
       <c r="J7" s="25"/>
       <c r="K7" s="25"/>
     </row>
-    <row r="8" spans="2:13" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:13" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="B8" s="43"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -10359,7 +10359,7 @@
       <c r="L8" s="92"/>
       <c r="M8" s="6"/>
     </row>
-    <row r="9" spans="2:13" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="s">
         <v>7</v>
       </c>
@@ -10397,7 +10397,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>14</v>
       </c>
@@ -10431,7 +10431,7 @@
       <c r="L10" s="22"/>
       <c r="M10" s="22"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>61</v>
       </c>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="M11" s="22"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
         <v>14</v>
       </c>
@@ -10501,7 +10501,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="22"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>14</v>
       </c>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="M13" s="22"/>
     </row>
-    <row r="14" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>14</v>
       </c>
@@ -10573,7 +10573,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>14</v>
       </c>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>14</v>
       </c>
@@ -10645,7 +10645,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>14</v>
       </c>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="M17" s="22"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>14</v>
       </c>
@@ -10715,7 +10715,7 @@
       <c r="L18" s="12"/>
       <c r="M18" s="22"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>14</v>
       </c>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="M19" s="22"/>
     </row>
-    <row r="20" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>14</v>
       </c>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="M20" s="22"/>
     </row>
-    <row r="21" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>14</v>
       </c>
@@ -10811,7 +10811,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="22" spans="2:13" ht="49.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:13" ht="48" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>14</v>
       </c>
@@ -10839,7 +10839,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>14</v>
       </c>
@@ -10861,7 +10861,7 @@
       <c r="L23" s="13"/>
       <c r="M23" s="22"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>14</v>
       </c>
@@ -10883,7 +10883,7 @@
       <c r="L24" s="13"/>
       <c r="M24" s="22"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>14</v>
       </c>
@@ -10905,7 +10905,7 @@
       <c r="L25" s="12"/>
       <c r="M25" s="30"/>
     </row>
-    <row r="26" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>14</v>
       </c>
@@ -10937,7 +10937,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="27" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>14</v>
       </c>
@@ -10969,7 +10969,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>14</v>
       </c>
@@ -10999,7 +10999,7 @@
       <c r="L28" s="12"/>
       <c r="M28" s="12"/>
     </row>
-    <row r="29" spans="2:13" ht="31.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>14</v>
       </c>
@@ -11027,7 +11027,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B30" s="14" t="s">
         <v>14</v>
       </c>
@@ -11047,7 +11047,7 @@
       <c r="L30" s="13"/>
       <c r="M30" s="30"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>14</v>
       </c>
@@ -11067,7 +11067,7 @@
       <c r="L31" s="12"/>
       <c r="M31" s="12"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>14</v>
       </c>
@@ -11087,7 +11087,7 @@
       <c r="L32" s="12"/>
       <c r="M32" s="22"/>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>14</v>
       </c>
@@ -11107,7 +11107,7 @@
       <c r="L33" s="12"/>
       <c r="M33" s="12"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>14</v>
       </c>
@@ -11127,7 +11127,7 @@
       <c r="L34" s="12"/>
       <c r="M34" s="12"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>14</v>
       </c>
@@ -11147,7 +11147,7 @@
       <c r="L35" s="13"/>
       <c r="M35" s="12"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>14</v>
       </c>
@@ -11167,7 +11167,7 @@
       <c r="L36" s="12"/>
       <c r="M36" s="22"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>14</v>
       </c>
@@ -11187,7 +11187,7 @@
       <c r="L37" s="13"/>
       <c r="M37" s="12"/>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>14</v>
       </c>
@@ -11207,7 +11207,7 @@
       <c r="L38" s="12"/>
       <c r="M38" s="22"/>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>14</v>
       </c>
@@ -11227,7 +11227,7 @@
       <c r="L39" s="12"/>
       <c r="M39" s="12"/>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>14</v>
       </c>
@@ -11247,7 +11247,7 @@
       <c r="L40" s="12"/>
       <c r="M40" s="12"/>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>14</v>
       </c>
@@ -11267,7 +11267,7 @@
       <c r="L41" s="12"/>
       <c r="M41" s="12"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42" s="9" t="s">
         <v>14</v>
       </c>
@@ -11287,7 +11287,7 @@
       <c r="L42" s="12"/>
       <c r="M42" s="12"/>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43" s="9" t="s">
         <v>14</v>
       </c>
@@ -11307,7 +11307,7 @@
       <c r="L43" s="12"/>
       <c r="M43" s="22"/>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44" s="9" t="s">
         <v>14</v>
       </c>
@@ -11327,7 +11327,7 @@
       <c r="L44" s="12"/>
       <c r="M44" s="22"/>
     </row>
-    <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45" s="9" t="s">
         <v>14</v>
       </c>
@@ -11351,7 +11351,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46" s="9" t="s">
         <v>14</v>
       </c>
@@ -11375,7 +11375,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B47" s="9" t="s">
         <v>14</v>
       </c>
@@ -11411,7 +11411,7 @@
       </c>
       <c r="M47" s="22"/>
     </row>
-    <row r="48" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B48" s="9" t="s">
         <v>14</v>
       </c>
@@ -11443,7 +11443,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B49" s="9" t="s">
         <v>14</v>
       </c>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="M49" s="22"/>
     </row>
-    <row r="50" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B50" s="9" t="s">
         <v>14</v>
       </c>
@@ -11511,7 +11511,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="51" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B51" s="9" t="s">
         <v>14</v>
       </c>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="M51" s="22"/>
     </row>
-    <row r="52" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B52" s="9" t="s">
         <v>14</v>
       </c>
@@ -11579,7 +11579,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="53" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="9" t="s">
         <v>14</v>
       </c>
@@ -11605,7 +11605,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="54" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B54" s="9" t="s">
         <v>14</v>
       </c>
@@ -11641,7 +11641,7 @@
       </c>
       <c r="M54" s="12"/>
     </row>
-    <row r="55" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B55" s="9" t="s">
         <v>14</v>
       </c>
@@ -11667,7 +11667,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B56" s="9" t="s">
         <v>14</v>
       </c>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="M56" s="22"/>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B57" s="9" t="s">
         <v>14</v>
       </c>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="M57" s="22"/>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B58" s="9" t="s">
         <v>61</v>
       </c>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="M58" s="22"/>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B59" s="9" t="s">
         <v>61</v>
       </c>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="M59" s="22"/>
     </row>
-    <row r="60" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B60" s="9" t="s">
         <v>14</v>
       </c>
@@ -11835,7 +11835,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B61" s="9" t="s">
         <v>14</v>
       </c>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="M61" s="12"/>
     </row>
-    <row r="62" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B62" s="9" t="s">
         <v>14</v>
       </c>
@@ -11909,7 +11909,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B63" s="9" t="s">
         <v>14</v>
       </c>
@@ -11945,7 +11945,7 @@
       </c>
       <c r="M63" s="22"/>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B64" s="9" t="s">
         <v>14</v>
       </c>
@@ -11979,7 +11979,7 @@
       <c r="L64" s="12"/>
       <c r="M64" s="22"/>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B65" s="9" t="s">
         <v>14</v>
       </c>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="M65" s="22"/>
     </row>
-    <row r="66" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B66" s="9" t="s">
         <v>14</v>
       </c>
@@ -12051,7 +12051,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="67" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B67" s="9" t="s">
         <v>14</v>
       </c>
@@ -12077,7 +12077,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B68" s="9" t="s">
         <v>14</v>
       </c>
@@ -12113,7 +12113,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B69" s="9" t="s">
         <v>14</v>
       </c>
@@ -12145,7 +12145,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B70" s="9" t="s">
         <v>14</v>
       </c>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="M70" s="22"/>
     </row>
-    <row r="71" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B71" s="9" t="s">
         <v>14</v>
       </c>
@@ -12207,7 +12207,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B72" s="9" t="s">
         <v>14</v>
       </c>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="M72" s="12"/>
     </row>
-    <row r="73" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B73" s="9" t="s">
         <v>14</v>
       </c>
@@ -12269,7 +12269,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B74" s="9" t="s">
         <v>14</v>
       </c>
@@ -12297,7 +12297,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="75" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B75" s="9" t="s">
         <v>14</v>
       </c>
@@ -12321,7 +12321,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="76" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B76" s="9" t="s">
         <v>61</v>
       </c>
@@ -12345,7 +12345,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B77" s="9" t="s">
         <v>61</v>
       </c>
@@ -12377,7 +12377,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="78" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B78" s="9" t="s">
         <v>61</v>
       </c>
@@ -12409,7 +12409,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="79" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B79" s="9" t="s">
         <v>61</v>
       </c>
@@ -12441,7 +12441,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B80" s="9" t="s">
         <v>14</v>
       </c>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="M80" s="12"/>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B81" s="9" t="s">
         <v>14</v>
       </c>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="M81" s="22"/>
     </row>
-    <row r="82" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B82" s="9" t="s">
         <v>14</v>
       </c>
@@ -12539,7 +12539,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B83" s="9" t="s">
         <v>88</v>
       </c>
@@ -12575,7 +12575,7 @@
       </c>
       <c r="M83" s="12"/>
     </row>
-    <row r="84" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B84" s="9" t="s">
         <v>88</v>
       </c>
@@ -12613,7 +12613,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B85" s="9" t="s">
         <v>88</v>
       </c>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="M85" s="12"/>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B86" s="9" t="s">
         <v>88</v>
       </c>
@@ -12685,7 +12685,7 @@
       </c>
       <c r="M86" s="12"/>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B87" s="9" t="s">
         <v>91</v>
       </c>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="M87" s="12"/>
     </row>
-    <row r="88" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B88" s="9" t="s">
         <v>91</v>
       </c>
@@ -12759,7 +12759,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="89" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B89" s="9" t="s">
         <v>91</v>
       </c>
@@ -12797,7 +12797,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B90" s="9" t="s">
         <v>88</v>
       </c>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="M90" s="12"/>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B91" s="9" t="s">
         <v>88</v>
       </c>
@@ -12869,7 +12869,7 @@
       </c>
       <c r="M91" s="12"/>
     </row>
-    <row r="92" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B92" s="9" t="s">
         <v>88</v>
       </c>
@@ -12905,7 +12905,7 @@
       </c>
       <c r="M92" s="12"/>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B93" s="9" t="s">
         <v>88</v>
       </c>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="M93" s="12"/>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B94" s="9" t="s">
         <v>88</v>
       </c>
@@ -12975,7 +12975,7 @@
       <c r="L94" s="12"/>
       <c r="M94" s="12"/>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B95" s="9" t="s">
         <v>88</v>
       </c>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="M95" s="12"/>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B96" s="9" t="s">
         <v>88</v>
       </c>
@@ -13045,7 +13045,7 @@
       <c r="L96" s="12"/>
       <c r="M96" s="12"/>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B97" s="9" t="s">
         <v>88</v>
       </c>
@@ -13079,7 +13079,7 @@
       <c r="L97" s="12"/>
       <c r="M97" s="12"/>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B98" s="9" t="s">
         <v>88</v>
       </c>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="M98" s="12"/>
     </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B99" s="9" t="s">
         <v>88</v>
       </c>
@@ -13149,7 +13149,7 @@
       <c r="L99" s="12"/>
       <c r="M99" s="12"/>
     </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B100" s="9" t="s">
         <v>88</v>
       </c>
@@ -13183,7 +13183,7 @@
       <c r="L100" s="12"/>
       <c r="M100" s="12"/>
     </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B101" s="9" t="s">
         <v>88</v>
       </c>
@@ -13219,7 +13219,7 @@
       </c>
       <c r="M101" s="12"/>
     </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B102" s="9" t="s">
         <v>88</v>
       </c>
@@ -13253,7 +13253,7 @@
       <c r="L102" s="12"/>
       <c r="M102" s="12"/>
     </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B103" s="9" t="s">
         <v>88</v>
       </c>
@@ -13287,7 +13287,7 @@
       <c r="L103" s="12"/>
       <c r="M103" s="12"/>
     </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B104" s="9" t="s">
         <v>88</v>
       </c>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="M104" s="12"/>
     </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B105" s="9" t="s">
         <v>88</v>
       </c>
@@ -13357,7 +13357,7 @@
       <c r="L105" s="12"/>
       <c r="M105" s="12"/>
     </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B106" s="9" t="s">
         <v>88</v>
       </c>
@@ -13391,7 +13391,7 @@
       <c r="L106" s="12"/>
       <c r="M106" s="12"/>
     </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B107" s="9" t="s">
         <v>88</v>
       </c>
@@ -13427,7 +13427,7 @@
       </c>
       <c r="M107" s="12"/>
     </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B108" s="9" t="s">
         <v>88</v>
       </c>
@@ -13461,7 +13461,7 @@
       <c r="L108" s="12"/>
       <c r="M108" s="12"/>
     </row>
-    <row r="109" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B109" s="9" t="s">
         <v>88</v>
       </c>
@@ -13495,7 +13495,7 @@
       <c r="L109" s="12"/>
       <c r="M109" s="12"/>
     </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B110" s="9" t="s">
         <v>88</v>
       </c>
@@ -13531,7 +13531,7 @@
       </c>
       <c r="M110" s="12"/>
     </row>
-    <row r="111" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B111" s="9" t="s">
         <v>88</v>
       </c>
@@ -13565,7 +13565,7 @@
       <c r="L111" s="12"/>
       <c r="M111" s="12"/>
     </row>
-    <row r="112" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B112" s="9" t="s">
         <v>88</v>
       </c>
@@ -13599,7 +13599,7 @@
       <c r="L112" s="12"/>
       <c r="M112" s="12"/>
     </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B113" s="9" t="s">
         <v>88</v>
       </c>
@@ -13635,7 +13635,7 @@
       </c>
       <c r="M113" s="12"/>
     </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B114" s="9" t="s">
         <v>88</v>
       </c>
@@ -13669,7 +13669,7 @@
       <c r="L114" s="12"/>
       <c r="M114" s="12"/>
     </row>
-    <row r="115" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B115" s="9" t="s">
         <v>88</v>
       </c>
@@ -13703,7 +13703,7 @@
       <c r="L115" s="12"/>
       <c r="M115" s="12"/>
     </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B116" s="9" t="s">
         <v>88</v>
       </c>
@@ -13739,7 +13739,7 @@
       </c>
       <c r="M116" s="12"/>
     </row>
-    <row r="117" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B117" s="9" t="s">
         <v>88</v>
       </c>
@@ -13773,7 +13773,7 @@
       <c r="L117" s="12"/>
       <c r="M117" s="12"/>
     </row>
-    <row r="118" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B118" s="9" t="s">
         <v>88</v>
       </c>
@@ -13807,7 +13807,7 @@
       <c r="L118" s="12"/>
       <c r="M118" s="12"/>
     </row>
-    <row r="119" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B119" s="9" t="s">
         <v>88</v>
       </c>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="M119" s="12"/>
     </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B120" s="9" t="s">
         <v>88</v>
       </c>
@@ -13877,7 +13877,7 @@
       <c r="L120" s="12"/>
       <c r="M120" s="12"/>
     </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B121" s="9" t="s">
         <v>88</v>
       </c>
@@ -13911,7 +13911,7 @@
       <c r="L121" s="12"/>
       <c r="M121" s="12"/>
     </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B122" s="9" t="s">
         <v>88</v>
       </c>
@@ -13939,7 +13939,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="123" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B123" s="9" t="s">
         <v>88</v>
       </c>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="M123" s="12"/>
     </row>
-    <row r="124" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B124" s="9" t="s">
         <v>88</v>
       </c>
@@ -14009,7 +14009,7 @@
       <c r="L124" s="12"/>
       <c r="M124" s="12"/>
     </row>
-    <row r="125" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B125" s="9" t="s">
         <v>88</v>
       </c>
@@ -14043,7 +14043,7 @@
       <c r="L125" s="12"/>
       <c r="M125" s="12"/>
     </row>
-    <row r="126" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B126" s="9" t="s">
         <v>88</v>
       </c>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="M126" s="12"/>
     </row>
-    <row r="127" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B127" s="9" t="s">
         <v>88</v>
       </c>
@@ -14113,7 +14113,7 @@
       <c r="L127" s="12"/>
       <c r="M127" s="12"/>
     </row>
-    <row r="128" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B128" s="9" t="s">
         <v>88</v>
       </c>
@@ -14147,7 +14147,7 @@
       <c r="L128" s="12"/>
       <c r="M128" s="12"/>
     </row>
-    <row r="129" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B129" s="9" t="s">
         <v>88</v>
       </c>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="M129" s="12"/>
     </row>
-    <row r="130" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B130" s="9" t="s">
         <v>88</v>
       </c>
@@ -14217,7 +14217,7 @@
       <c r="L130" s="12"/>
       <c r="M130" s="12"/>
     </row>
-    <row r="131" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B131" s="9" t="s">
         <v>88</v>
       </c>
@@ -14251,7 +14251,7 @@
       <c r="L131" s="12"/>
       <c r="M131" s="12"/>
     </row>
-    <row r="132" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B132" s="9" t="s">
         <v>88</v>
       </c>
@@ -14283,7 +14283,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="133" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B133" s="9" t="s">
         <v>88</v>
       </c>
@@ -14317,7 +14317,7 @@
       <c r="L133" s="12"/>
       <c r="M133" s="12"/>
     </row>
-    <row r="134" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B134" s="9" t="s">
         <v>88</v>
       </c>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="M134" s="12"/>
     </row>
-    <row r="135" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B135" s="9" t="s">
         <v>88</v>
       </c>
@@ -14387,7 +14387,7 @@
       <c r="L135" s="12"/>
       <c r="M135" s="12"/>
     </row>
-    <row r="136" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B136" s="9" t="s">
         <v>88</v>
       </c>
@@ -14423,7 +14423,7 @@
       </c>
       <c r="M136" s="12"/>
     </row>
-    <row r="137" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B137" s="9" t="s">
         <v>88</v>
       </c>
@@ -14457,7 +14457,7 @@
       <c r="L137" s="12"/>
       <c r="M137" s="12"/>
     </row>
-    <row r="138" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B138" s="9" t="s">
         <v>88</v>
       </c>
@@ -14491,7 +14491,7 @@
       <c r="L138" s="12"/>
       <c r="M138" s="12"/>
     </row>
-    <row r="139" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B139" s="9" t="s">
         <v>88</v>
       </c>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M139" s="12"/>
     </row>
-    <row r="140" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B140" s="9" t="s">
         <v>88</v>
       </c>
@@ -14561,7 +14561,7 @@
       <c r="L140" s="12"/>
       <c r="M140" s="12"/>
     </row>
-    <row r="141" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B141" s="9" t="s">
         <v>88</v>
       </c>
@@ -14595,7 +14595,7 @@
       <c r="L141" s="12"/>
       <c r="M141" s="12"/>
     </row>
-    <row r="142" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B142" s="9" t="s">
         <v>91</v>
       </c>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="M142" s="12"/>
     </row>
-    <row r="143" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B143" s="9" t="s">
         <v>91</v>
       </c>
@@ -14665,7 +14665,7 @@
       <c r="L143" s="12"/>
       <c r="M143" s="12"/>
     </row>
-    <row r="144" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B144" s="9" t="s">
         <v>91</v>
       </c>
@@ -14699,7 +14699,7 @@
       <c r="L144" s="12"/>
       <c r="M144" s="12"/>
     </row>
-    <row r="145" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B145" s="9" t="s">
         <v>88</v>
       </c>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="M145" s="12"/>
     </row>
-    <row r="146" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B146" s="9" t="s">
         <v>88</v>
       </c>
@@ -14769,7 +14769,7 @@
       <c r="L146" s="12"/>
       <c r="M146" s="12"/>
     </row>
-    <row r="147" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B147" s="9" t="s">
         <v>88</v>
       </c>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="M147" s="12"/>
     </row>
-    <row r="148" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B148" s="9" t="s">
         <v>88</v>
       </c>
@@ -14839,7 +14839,7 @@
       <c r="L148" s="12"/>
       <c r="M148" s="12"/>
     </row>
-    <row r="149" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B149" s="9" t="s">
         <v>88</v>
       </c>
@@ -14873,7 +14873,7 @@
       <c r="L149" s="12"/>
       <c r="M149" s="12"/>
     </row>
-    <row r="150" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B150" s="9" t="s">
         <v>88</v>
       </c>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="M150" s="12"/>
     </row>
-    <row r="151" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B151" s="9" t="s">
         <v>88</v>
       </c>
@@ -14947,7 +14947,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="152" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B152" s="9" t="s">
         <v>88</v>
       </c>
@@ -14983,7 +14983,7 @@
       </c>
       <c r="M152" s="12"/>
     </row>
-    <row r="153" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B153" s="9" t="s">
         <v>88</v>
       </c>
@@ -15017,7 +15017,7 @@
       <c r="L153" s="31"/>
       <c r="M153" s="12"/>
     </row>
-    <row r="154" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B154" s="9" t="s">
         <v>88</v>
       </c>
@@ -15051,7 +15051,7 @@
       <c r="L154" s="31"/>
       <c r="M154" s="12"/>
     </row>
-    <row r="155" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B155" s="49" t="s">
         <v>88</v>
       </c>
@@ -15073,7 +15073,7 @@
       <c r="L155" s="31"/>
       <c r="M155" s="12"/>
     </row>
-    <row r="156" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B156" s="49" t="s">
         <v>88</v>
       </c>
@@ -15109,7 +15109,7 @@
       </c>
       <c r="M156" s="12"/>
     </row>
-    <row r="157" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B157" s="49" t="s">
         <v>88</v>
       </c>
@@ -15143,7 +15143,7 @@
       <c r="L157" s="12"/>
       <c r="M157" s="12"/>
     </row>
-    <row r="158" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B158" s="49" t="s">
         <v>88</v>
       </c>
@@ -15177,7 +15177,7 @@
       <c r="L158" s="12"/>
       <c r="M158" s="12"/>
     </row>
-    <row r="159" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B159" s="49" t="s">
         <v>88</v>
       </c>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="M159" s="12"/>
     </row>
-    <row r="160" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B160" s="49" t="s">
         <v>88</v>
       </c>
@@ -15247,7 +15247,7 @@
       <c r="L160" s="12"/>
       <c r="M160" s="12"/>
     </row>
-    <row r="161" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B161" s="49" t="s">
         <v>88</v>
       </c>
@@ -15281,7 +15281,7 @@
       <c r="L161" s="12"/>
       <c r="M161" s="12"/>
     </row>
-    <row r="162" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B162" s="9" t="s">
         <v>88</v>
       </c>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="M162" s="12"/>
     </row>
-    <row r="163" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B163" s="9" t="s">
         <v>88</v>
       </c>
@@ -15351,7 +15351,7 @@
       <c r="L163" s="12"/>
       <c r="M163" s="12"/>
     </row>
-    <row r="164" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B164" s="9" t="s">
         <v>88</v>
       </c>
@@ -15385,7 +15385,7 @@
       <c r="L164" s="12"/>
       <c r="M164" s="12"/>
     </row>
-    <row r="165" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B165" s="49" t="s">
         <v>88</v>
       </c>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="M165" s="12"/>
     </row>
-    <row r="166" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B166" s="49" t="s">
         <v>88</v>
       </c>
@@ -15455,7 +15455,7 @@
       <c r="L166" s="31"/>
       <c r="M166" s="31"/>
     </row>
-    <row r="167" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B167" s="49" t="s">
         <v>88</v>
       </c>
@@ -15489,7 +15489,7 @@
       <c r="L167" s="31"/>
       <c r="M167" s="31"/>
     </row>
-    <row r="168" spans="2:13" ht="15" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B168" s="49" t="s">
         <v>91</v>
       </c>
@@ -15521,7 +15521,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="169" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B169" s="52" t="s">
         <v>91</v>
       </c>
@@ -15574,16 +15574,16 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A2:E10"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="1.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="3" customWidth="1"/>
     <col min="3" max="3" width="82" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="85.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="85.85546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
         <v>679</v>
       </c>
@@ -15591,14 +15591,14 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="1:5" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
         <v>8</v>
       </c>
@@ -15612,7 +15612,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B5" s="84" t="s">
         <v>419</v>
       </c>
@@ -15622,7 +15622,7 @@
       <c r="D5" s="85"/>
       <c r="E5" s="86"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" s="84" t="s">
         <v>420</v>
       </c>
@@ -15632,7 +15632,7 @@
       <c r="D6" s="85"/>
       <c r="E6" s="87"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" s="84" t="s">
         <v>421</v>
       </c>
@@ -15642,7 +15642,7 @@
       <c r="D7" s="85"/>
       <c r="E7" s="87"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" s="84" t="s">
         <v>422</v>
       </c>
@@ -15652,7 +15652,7 @@
       <c r="D8" s="85"/>
       <c r="E8" s="87"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" s="84" t="s">
         <v>437</v>
       </c>
@@ -15662,7 +15662,7 @@
       <c r="D9" s="85"/>
       <c r="E9" s="87"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C10" s="91"/>
     </row>
   </sheetData>
@@ -15678,16 +15678,16 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A2:G96"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="36.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="85.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="36.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="85.85546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
         <v>679</v>
       </c>
@@ -15695,14 +15695,14 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:7" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="1:7" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
         <v>8</v>
       </c>
@@ -15716,7 +15716,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="18" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="17.25" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B5" s="78" t="s">
         <v>419</v>
       </c>
@@ -15729,7 +15729,7 @@
       </c>
       <c r="E5" s="68"/>
     </row>
-    <row r="6" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B6" s="73" t="s">
         <v>420</v>
       </c>
@@ -15742,7 +15742,7 @@
       </c>
       <c r="E6" s="67"/>
     </row>
-    <row r="7" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B7" s="73" t="s">
         <v>421</v>
       </c>
@@ -15755,7 +15755,7 @@
       </c>
       <c r="E7" s="67"/>
     </row>
-    <row r="8" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B8" s="73" t="s">
         <v>422</v>
       </c>
@@ -15768,7 +15768,7 @@
       </c>
       <c r="E8" s="67"/>
     </row>
-    <row r="9" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="73" t="s">
         <v>437</v>
       </c>
@@ -15781,7 +15781,7 @@
       </c>
       <c r="E9" s="67"/>
     </row>
-    <row r="10" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B10" s="73" t="s">
         <v>438</v>
       </c>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="E10" s="67"/>
     </row>
-    <row r="11" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B11" s="73" t="s">
         <v>439</v>
       </c>
@@ -15807,7 +15807,7 @@
       </c>
       <c r="E11" s="67"/>
     </row>
-    <row r="12" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B12" s="73" t="s">
         <v>481</v>
       </c>
@@ -15820,7 +15820,7 @@
       </c>
       <c r="E12" s="67"/>
     </row>
-    <row r="13" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B13" s="73" t="s">
         <v>482</v>
       </c>
@@ -15834,7 +15834,7 @@
       <c r="E13" s="67"/>
       <c r="G13" s="40"/>
     </row>
-    <row r="14" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B14" s="73" t="s">
         <v>440</v>
       </c>
@@ -15848,7 +15848,7 @@
       <c r="E14" s="67"/>
       <c r="G14" s="40"/>
     </row>
-    <row r="15" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B15" s="73" t="s">
         <v>435</v>
       </c>
@@ -15862,7 +15862,7 @@
       <c r="E15" s="67"/>
       <c r="G15" s="40"/>
     </row>
-    <row r="16" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="73" t="s">
         <v>483</v>
       </c>
@@ -15876,7 +15876,7 @@
       <c r="E16" s="67"/>
       <c r="G16" s="40"/>
     </row>
-    <row r="17" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B17" s="73" t="s">
         <v>441</v>
       </c>
@@ -15890,7 +15890,7 @@
       <c r="E17" s="67"/>
       <c r="G17" s="40"/>
     </row>
-    <row r="18" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B18" s="73" t="s">
         <v>406</v>
       </c>
@@ -15904,7 +15904,7 @@
       <c r="E18" s="67"/>
       <c r="G18" s="40"/>
     </row>
-    <row r="19" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="73" t="s">
         <v>442</v>
       </c>
@@ -15918,7 +15918,7 @@
       <c r="E19" s="67"/>
       <c r="G19" s="40"/>
     </row>
-    <row r="20" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B20" s="73" t="s">
         <v>443</v>
       </c>
@@ -15932,7 +15932,7 @@
       <c r="E20" s="67"/>
       <c r="G20" s="40"/>
     </row>
-    <row r="21" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B21" s="73" t="s">
         <v>444</v>
       </c>
@@ -15946,7 +15946,7 @@
       <c r="E21" s="67"/>
       <c r="G21" s="40"/>
     </row>
-    <row r="22" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B22" s="73" t="s">
         <v>403</v>
       </c>
@@ -15960,7 +15960,7 @@
       <c r="E22" s="67"/>
       <c r="G22" s="40"/>
     </row>
-    <row r="23" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B23" s="73" t="s">
         <v>445</v>
       </c>
@@ -15974,7 +15974,7 @@
       <c r="E23" s="67"/>
       <c r="G23" s="40"/>
     </row>
-    <row r="24" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B24" s="73" t="s">
         <v>407</v>
       </c>
@@ -15988,7 +15988,7 @@
       <c r="E24" s="67"/>
       <c r="G24" s="40"/>
     </row>
-    <row r="25" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B25" s="73" t="s">
         <v>446</v>
       </c>
@@ -16002,7 +16002,7 @@
       <c r="E25" s="67"/>
       <c r="G25" s="40"/>
     </row>
-    <row r="26" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B26" s="73" t="s">
         <v>404</v>
       </c>
@@ -16016,7 +16016,7 @@
       <c r="E26" s="67"/>
       <c r="G26" s="40"/>
     </row>
-    <row r="27" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B27" s="73" t="s">
         <v>484</v>
       </c>
@@ -16030,7 +16030,7 @@
       <c r="E27" s="67"/>
       <c r="G27" s="40"/>
     </row>
-    <row r="28" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B28" s="73" t="s">
         <v>447</v>
       </c>
@@ -16044,7 +16044,7 @@
       <c r="E28" s="67"/>
       <c r="G28" s="40"/>
     </row>
-    <row r="29" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B29" s="73" t="s">
         <v>448</v>
       </c>
@@ -16058,7 +16058,7 @@
       <c r="E29" s="67"/>
       <c r="G29" s="40"/>
     </row>
-    <row r="30" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B30" s="73" t="s">
         <v>449</v>
       </c>
@@ -16072,7 +16072,7 @@
       <c r="E30" s="67"/>
       <c r="G30" s="40"/>
     </row>
-    <row r="31" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B31" s="73" t="s">
         <v>488</v>
       </c>
@@ -16086,7 +16086,7 @@
       <c r="E31" s="67"/>
       <c r="G31" s="40"/>
     </row>
-    <row r="32" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B32" s="73" t="s">
         <v>450</v>
       </c>
@@ -16100,7 +16100,7 @@
       <c r="E32" s="67"/>
       <c r="G32" s="40"/>
     </row>
-    <row r="33" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B33" s="73" t="s">
         <v>408</v>
       </c>
@@ -16114,7 +16114,7 @@
       <c r="E33" s="67"/>
       <c r="G33" s="40"/>
     </row>
-    <row r="34" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B34" s="73" t="s">
         <v>451</v>
       </c>
@@ -16128,7 +16128,7 @@
       <c r="E34" s="67"/>
       <c r="G34" s="40"/>
     </row>
-    <row r="35" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B35" s="73" t="s">
         <v>432</v>
       </c>
@@ -16142,7 +16142,7 @@
       <c r="E35" s="67"/>
       <c r="G35" s="40"/>
     </row>
-    <row r="36" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B36" s="73" t="s">
         <v>452</v>
       </c>
@@ -16156,7 +16156,7 @@
       <c r="E36" s="67"/>
       <c r="G36" s="40"/>
     </row>
-    <row r="37" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B37" s="73" t="s">
         <v>453</v>
       </c>
@@ -16170,7 +16170,7 @@
       <c r="E37" s="67"/>
       <c r="G37" s="40"/>
     </row>
-    <row r="38" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B38" s="73" t="s">
         <v>454</v>
       </c>
@@ -16184,7 +16184,7 @@
       <c r="E38" s="67"/>
       <c r="G38" s="40"/>
     </row>
-    <row r="39" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B39" s="73" t="s">
         <v>409</v>
       </c>
@@ -16198,7 +16198,7 @@
       <c r="E39" s="67"/>
       <c r="G39" s="40"/>
     </row>
-    <row r="40" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B40" s="73" t="s">
         <v>478</v>
       </c>
@@ -16212,7 +16212,7 @@
       <c r="E40" s="67"/>
       <c r="G40" s="40"/>
     </row>
-    <row r="41" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B41" s="73" t="s">
         <v>434</v>
       </c>
@@ -16226,7 +16226,7 @@
       <c r="E41" s="67"/>
       <c r="G41" s="40"/>
     </row>
-    <row r="42" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B42" s="73" t="s">
         <v>431</v>
       </c>
@@ -16240,7 +16240,7 @@
       <c r="E42" s="67"/>
       <c r="G42" s="40"/>
     </row>
-    <row r="43" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B43" s="73" t="s">
         <v>455</v>
       </c>
@@ -16254,7 +16254,7 @@
       <c r="E43" s="67"/>
       <c r="G43" s="40"/>
     </row>
-    <row r="44" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B44" s="73" t="s">
         <v>456</v>
       </c>
@@ -16268,7 +16268,7 @@
       <c r="E44" s="67"/>
       <c r="G44" s="40"/>
     </row>
-    <row r="45" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B45" s="73" t="s">
         <v>457</v>
       </c>
@@ -16282,7 +16282,7 @@
       <c r="E45" s="67"/>
       <c r="G45" s="40"/>
     </row>
-    <row r="46" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B46" s="73" t="s">
         <v>458</v>
       </c>
@@ -16296,7 +16296,7 @@
       <c r="E46" s="67"/>
       <c r="G46" s="40"/>
     </row>
-    <row r="47" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B47" s="73" t="s">
         <v>433</v>
       </c>
@@ -16310,7 +16310,7 @@
       <c r="E47" s="67"/>
       <c r="G47" s="40"/>
     </row>
-    <row r="48" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B48" s="73" t="s">
         <v>479</v>
       </c>
@@ -16324,7 +16324,7 @@
       <c r="E48" s="67"/>
       <c r="G48" s="40"/>
     </row>
-    <row r="49" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B49" s="73" t="s">
         <v>459</v>
       </c>
@@ -16338,7 +16338,7 @@
       <c r="E49" s="67"/>
       <c r="G49" s="40"/>
     </row>
-    <row r="50" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B50" s="73" t="s">
         <v>480</v>
       </c>
@@ -16352,7 +16352,7 @@
       <c r="E50" s="67"/>
       <c r="G50" s="40"/>
     </row>
-    <row r="51" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B51" s="73" t="s">
         <v>428</v>
       </c>
@@ -16366,7 +16366,7 @@
       <c r="E51" s="67"/>
       <c r="G51" s="40"/>
     </row>
-    <row r="52" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B52" s="73" t="s">
         <v>485</v>
       </c>
@@ -16380,7 +16380,7 @@
       <c r="E52" s="67"/>
       <c r="G52" s="40"/>
     </row>
-    <row r="53" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B53" s="73" t="s">
         <v>460</v>
       </c>
@@ -16394,7 +16394,7 @@
       <c r="E53" s="67"/>
       <c r="G53" s="40"/>
     </row>
-    <row r="54" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B54" s="73" t="s">
         <v>486</v>
       </c>
@@ -16408,7 +16408,7 @@
       <c r="E54" s="67"/>
       <c r="G54" s="40"/>
     </row>
-    <row r="55" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B55" s="73" t="s">
         <v>491</v>
       </c>
@@ -16422,7 +16422,7 @@
       <c r="E55" s="67"/>
       <c r="G55" s="40"/>
     </row>
-    <row r="56" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B56" s="73" t="s">
         <v>461</v>
       </c>
@@ -16436,7 +16436,7 @@
       <c r="E56" s="67"/>
       <c r="G56" s="40"/>
     </row>
-    <row r="57" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B57" s="73" t="s">
         <v>462</v>
       </c>
@@ -16450,7 +16450,7 @@
       <c r="E57" s="67"/>
       <c r="G57" s="40"/>
     </row>
-    <row r="58" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B58" s="73" t="s">
         <v>410</v>
       </c>
@@ -16464,7 +16464,7 @@
       <c r="E58" s="67"/>
       <c r="G58" s="40"/>
     </row>
-    <row r="59" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B59" s="73" t="s">
         <v>463</v>
       </c>
@@ -16478,7 +16478,7 @@
       <c r="E59" s="67"/>
       <c r="G59" s="40"/>
     </row>
-    <row r="60" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B60" s="73" t="s">
         <v>492</v>
       </c>
@@ -16492,7 +16492,7 @@
       <c r="E60" s="69"/>
       <c r="G60" s="40"/>
     </row>
-    <row r="61" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B61" s="73" t="s">
         <v>429</v>
       </c>
@@ -16506,7 +16506,7 @@
       <c r="E61" s="69"/>
       <c r="G61" s="40"/>
     </row>
-    <row r="62" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B62" s="73" t="s">
         <v>464</v>
       </c>
@@ -16520,7 +16520,7 @@
       <c r="E62" s="69"/>
       <c r="G62" s="40"/>
     </row>
-    <row r="63" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B63" s="73" t="s">
         <v>430</v>
       </c>
@@ -16534,7 +16534,7 @@
       <c r="E63" s="69"/>
       <c r="G63" s="40"/>
     </row>
-    <row r="64" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B64" s="73" t="s">
         <v>487</v>
       </c>
@@ -16548,7 +16548,7 @@
       <c r="E64" s="69"/>
       <c r="G64" s="40"/>
     </row>
-    <row r="65" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B65" s="73" t="s">
         <v>416</v>
       </c>
@@ -16562,7 +16562,7 @@
       <c r="E65" s="69"/>
       <c r="G65" s="40"/>
     </row>
-    <row r="66" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B66" s="73" t="s">
         <v>411</v>
       </c>
@@ -16576,7 +16576,7 @@
       <c r="E66" s="69"/>
       <c r="G66" s="40"/>
     </row>
-    <row r="67" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B67" s="73" t="s">
         <v>465</v>
       </c>
@@ -16590,7 +16590,7 @@
       <c r="E67" s="69"/>
       <c r="G67" s="40"/>
     </row>
-    <row r="68" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B68" s="73" t="s">
         <v>466</v>
       </c>
@@ -16604,7 +16604,7 @@
       <c r="E68" s="69"/>
       <c r="G68" s="40"/>
     </row>
-    <row r="69" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B69" s="73" t="s">
         <v>467</v>
       </c>
@@ -16618,7 +16618,7 @@
       <c r="E69" s="67"/>
       <c r="G69" s="40"/>
     </row>
-    <row r="70" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B70" s="73" t="s">
         <v>468</v>
       </c>
@@ -16632,7 +16632,7 @@
       <c r="E70" s="67"/>
       <c r="G70" s="40"/>
     </row>
-    <row r="71" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B71" s="73" t="s">
         <v>469</v>
       </c>
@@ -16646,7 +16646,7 @@
       <c r="E71" s="67"/>
       <c r="G71" s="40"/>
     </row>
-    <row r="72" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B72" s="73" t="s">
         <v>418</v>
       </c>
@@ -16660,7 +16660,7 @@
       <c r="E72" s="67"/>
       <c r="G72" s="40"/>
     </row>
-    <row r="73" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B73" s="73" t="s">
         <v>470</v>
       </c>
@@ -16674,7 +16674,7 @@
       <c r="E73" s="67"/>
       <c r="G73" s="40"/>
     </row>
-    <row r="74" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B74" s="73" t="s">
         <v>425</v>
       </c>
@@ -16688,7 +16688,7 @@
       <c r="E74" s="70"/>
       <c r="G74" s="40"/>
     </row>
-    <row r="75" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B75" s="73" t="s">
         <v>426</v>
       </c>
@@ -16702,7 +16702,7 @@
       <c r="E75" s="67"/>
       <c r="G75" s="40"/>
     </row>
-    <row r="76" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B76" s="73" t="s">
         <v>412</v>
       </c>
@@ -16716,7 +16716,7 @@
       <c r="E76" s="67"/>
       <c r="G76" s="40"/>
     </row>
-    <row r="77" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B77" s="73" t="s">
         <v>471</v>
       </c>
@@ -16730,7 +16730,7 @@
       <c r="E77" s="67"/>
       <c r="G77" s="40"/>
     </row>
-    <row r="78" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B78" s="73" t="s">
         <v>405</v>
       </c>
@@ -16744,7 +16744,7 @@
       <c r="E78" s="67"/>
       <c r="G78" s="40"/>
     </row>
-    <row r="79" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B79" s="73" t="s">
         <v>413</v>
       </c>
@@ -16757,7 +16757,7 @@
       </c>
       <c r="E79" s="67"/>
     </row>
-    <row r="80" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B80" s="73" t="s">
         <v>472</v>
       </c>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="E80" s="67"/>
     </row>
-    <row r="81" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B81" s="73" t="s">
         <v>473</v>
       </c>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="E81" s="67"/>
     </row>
-    <row r="82" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B82" s="73" t="s">
         <v>474</v>
       </c>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="E82" s="67"/>
     </row>
-    <row r="83" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B83" s="73" t="s">
         <v>475</v>
       </c>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="E83" s="67"/>
     </row>
-    <row r="84" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B84" s="73" t="s">
         <v>436</v>
       </c>
@@ -16822,7 +16822,7 @@
       </c>
       <c r="E84" s="67"/>
     </row>
-    <row r="85" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B85" s="73" t="s">
         <v>476</v>
       </c>
@@ -16835,7 +16835,7 @@
       </c>
       <c r="E85" s="67"/>
     </row>
-    <row r="86" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B86" s="73" t="s">
         <v>402</v>
       </c>
@@ -16848,7 +16848,7 @@
       </c>
       <c r="E86" s="67"/>
     </row>
-    <row r="87" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B87" s="73" t="s">
         <v>427</v>
       </c>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="E87" s="67"/>
     </row>
-    <row r="88" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B88" s="73" t="s">
         <v>417</v>
       </c>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="E88" s="67"/>
     </row>
-    <row r="89" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B89" s="73" t="s">
         <v>423</v>
       </c>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="E89" s="67"/>
     </row>
-    <row r="90" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B90" s="73" t="s">
         <v>424</v>
       </c>
@@ -16900,7 +16900,7 @@
       </c>
       <c r="E90" s="67"/>
     </row>
-    <row r="91" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B91" s="73" t="s">
         <v>477</v>
       </c>
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E91" s="67"/>
     </row>
-    <row r="92" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B92" s="73" t="s">
         <v>414</v>
       </c>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="E92" s="67"/>
     </row>
-    <row r="93" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B93" s="73" t="s">
         <v>415</v>
       </c>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="E93" s="67"/>
     </row>
-    <row r="94" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B94" s="73" t="s">
         <v>489</v>
       </c>
@@ -16952,7 +16952,7 @@
       </c>
       <c r="E94" s="67"/>
     </row>
-    <row r="95" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B95" s="73" t="s">
         <v>490</v>
       </c>
@@ -16965,7 +16965,7 @@
       </c>
       <c r="E95" s="67"/>
     </row>
-    <row r="96" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B96" s="74" t="s">
         <v>401</v>
       </c>
@@ -17003,16 +17003,16 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A2:G96"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="36.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="85.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="36.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="85.85546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
         <v>679</v>
       </c>
@@ -17020,14 +17020,14 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:7" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="1:7" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
         <v>8</v>
       </c>
@@ -17041,7 +17041,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="18" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="17.25" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B5" s="72" t="s">
         <v>419</v>
       </c>
@@ -17054,7 +17054,7 @@
       </c>
       <c r="E5" s="68"/>
     </row>
-    <row r="6" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B6" s="73" t="s">
         <v>420</v>
       </c>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="E6" s="67"/>
     </row>
-    <row r="7" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B7" s="73" t="s">
         <v>421</v>
       </c>
@@ -17080,7 +17080,7 @@
       </c>
       <c r="E7" s="67"/>
     </row>
-    <row r="8" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B8" s="73" t="s">
         <v>422</v>
       </c>
@@ -17093,7 +17093,7 @@
       </c>
       <c r="E8" s="67"/>
     </row>
-    <row r="9" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="73" t="s">
         <v>437</v>
       </c>
@@ -17106,7 +17106,7 @@
       </c>
       <c r="E9" s="67"/>
     </row>
-    <row r="10" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B10" s="73" t="s">
         <v>438</v>
       </c>
@@ -17119,7 +17119,7 @@
       </c>
       <c r="E10" s="67"/>
     </row>
-    <row r="11" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B11" s="73" t="s">
         <v>439</v>
       </c>
@@ -17132,7 +17132,7 @@
       </c>
       <c r="E11" s="67"/>
     </row>
-    <row r="12" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B12" s="73" t="s">
         <v>481</v>
       </c>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="E12" s="67"/>
     </row>
-    <row r="13" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B13" s="73" t="s">
         <v>482</v>
       </c>
@@ -17159,7 +17159,7 @@
       <c r="E13" s="67"/>
       <c r="G13" s="40"/>
     </row>
-    <row r="14" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B14" s="73" t="s">
         <v>440</v>
       </c>
@@ -17173,7 +17173,7 @@
       <c r="E14" s="67"/>
       <c r="G14" s="40"/>
     </row>
-    <row r="15" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B15" s="73" t="s">
         <v>435</v>
       </c>
@@ -17187,7 +17187,7 @@
       <c r="E15" s="67"/>
       <c r="G15" s="40"/>
     </row>
-    <row r="16" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="73" t="s">
         <v>483</v>
       </c>
@@ -17201,7 +17201,7 @@
       <c r="E16" s="67"/>
       <c r="G16" s="40"/>
     </row>
-    <row r="17" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B17" s="73" t="s">
         <v>441</v>
       </c>
@@ -17215,7 +17215,7 @@
       <c r="E17" s="67"/>
       <c r="G17" s="40"/>
     </row>
-    <row r="18" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B18" s="73" t="s">
         <v>406</v>
       </c>
@@ -17229,7 +17229,7 @@
       <c r="E18" s="67"/>
       <c r="G18" s="40"/>
     </row>
-    <row r="19" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="73" t="s">
         <v>442</v>
       </c>
@@ -17243,7 +17243,7 @@
       <c r="E19" s="67"/>
       <c r="G19" s="40"/>
     </row>
-    <row r="20" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B20" s="73" t="s">
         <v>443</v>
       </c>
@@ -17257,7 +17257,7 @@
       <c r="E20" s="67"/>
       <c r="G20" s="40"/>
     </row>
-    <row r="21" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B21" s="73" t="s">
         <v>444</v>
       </c>
@@ -17271,7 +17271,7 @@
       <c r="E21" s="67"/>
       <c r="G21" s="40"/>
     </row>
-    <row r="22" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B22" s="73" t="s">
         <v>403</v>
       </c>
@@ -17285,7 +17285,7 @@
       <c r="E22" s="67"/>
       <c r="G22" s="40"/>
     </row>
-    <row r="23" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B23" s="73" t="s">
         <v>445</v>
       </c>
@@ -17299,7 +17299,7 @@
       <c r="E23" s="67"/>
       <c r="G23" s="40"/>
     </row>
-    <row r="24" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B24" s="73" t="s">
         <v>407</v>
       </c>
@@ -17313,7 +17313,7 @@
       <c r="E24" s="67"/>
       <c r="G24" s="40"/>
     </row>
-    <row r="25" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B25" s="73" t="s">
         <v>446</v>
       </c>
@@ -17327,7 +17327,7 @@
       <c r="E25" s="67"/>
       <c r="G25" s="40"/>
     </row>
-    <row r="26" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B26" s="73" t="s">
         <v>404</v>
       </c>
@@ -17341,7 +17341,7 @@
       <c r="E26" s="67"/>
       <c r="G26" s="40"/>
     </row>
-    <row r="27" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B27" s="73" t="s">
         <v>484</v>
       </c>
@@ -17355,7 +17355,7 @@
       <c r="E27" s="67"/>
       <c r="G27" s="40"/>
     </row>
-    <row r="28" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B28" s="73" t="s">
         <v>447</v>
       </c>
@@ -17369,7 +17369,7 @@
       <c r="E28" s="67"/>
       <c r="G28" s="40"/>
     </row>
-    <row r="29" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B29" s="73" t="s">
         <v>448</v>
       </c>
@@ -17383,7 +17383,7 @@
       <c r="E29" s="67"/>
       <c r="G29" s="40"/>
     </row>
-    <row r="30" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B30" s="73" t="s">
         <v>449</v>
       </c>
@@ -17397,7 +17397,7 @@
       <c r="E30" s="67"/>
       <c r="G30" s="40"/>
     </row>
-    <row r="31" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B31" s="73" t="s">
         <v>488</v>
       </c>
@@ -17411,7 +17411,7 @@
       <c r="E31" s="67"/>
       <c r="G31" s="40"/>
     </row>
-    <row r="32" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B32" s="73" t="s">
         <v>450</v>
       </c>
@@ -17425,7 +17425,7 @@
       <c r="E32" s="67"/>
       <c r="G32" s="40"/>
     </row>
-    <row r="33" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B33" s="73" t="s">
         <v>408</v>
       </c>
@@ -17439,7 +17439,7 @@
       <c r="E33" s="67"/>
       <c r="G33" s="40"/>
     </row>
-    <row r="34" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B34" s="73" t="s">
         <v>451</v>
       </c>
@@ -17453,7 +17453,7 @@
       <c r="E34" s="67"/>
       <c r="G34" s="40"/>
     </row>
-    <row r="35" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B35" s="73" t="s">
         <v>432</v>
       </c>
@@ -17467,7 +17467,7 @@
       <c r="E35" s="67"/>
       <c r="G35" s="40"/>
     </row>
-    <row r="36" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B36" s="73" t="s">
         <v>452</v>
       </c>
@@ -17481,7 +17481,7 @@
       <c r="E36" s="67"/>
       <c r="G36" s="40"/>
     </row>
-    <row r="37" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B37" s="73" t="s">
         <v>453</v>
       </c>
@@ -17495,7 +17495,7 @@
       <c r="E37" s="67"/>
       <c r="G37" s="40"/>
     </row>
-    <row r="38" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B38" s="73" t="s">
         <v>454</v>
       </c>
@@ -17509,7 +17509,7 @@
       <c r="E38" s="67"/>
       <c r="G38" s="40"/>
     </row>
-    <row r="39" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B39" s="73" t="s">
         <v>409</v>
       </c>
@@ -17523,7 +17523,7 @@
       <c r="E39" s="67"/>
       <c r="G39" s="40"/>
     </row>
-    <row r="40" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B40" s="73" t="s">
         <v>478</v>
       </c>
@@ -17537,7 +17537,7 @@
       <c r="E40" s="67"/>
       <c r="G40" s="40"/>
     </row>
-    <row r="41" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B41" s="73" t="s">
         <v>434</v>
       </c>
@@ -17551,7 +17551,7 @@
       <c r="E41" s="67"/>
       <c r="G41" s="40"/>
     </row>
-    <row r="42" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B42" s="73" t="s">
         <v>431</v>
       </c>
@@ -17565,7 +17565,7 @@
       <c r="E42" s="67"/>
       <c r="G42" s="40"/>
     </row>
-    <row r="43" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B43" s="73" t="s">
         <v>455</v>
       </c>
@@ -17579,7 +17579,7 @@
       <c r="E43" s="67"/>
       <c r="G43" s="40"/>
     </row>
-    <row r="44" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B44" s="73" t="s">
         <v>456</v>
       </c>
@@ -17593,7 +17593,7 @@
       <c r="E44" s="67"/>
       <c r="G44" s="40"/>
     </row>
-    <row r="45" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B45" s="73" t="s">
         <v>457</v>
       </c>
@@ -17607,7 +17607,7 @@
       <c r="E45" s="67"/>
       <c r="G45" s="40"/>
     </row>
-    <row r="46" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B46" s="73" t="s">
         <v>458</v>
       </c>
@@ -17621,7 +17621,7 @@
       <c r="E46" s="67"/>
       <c r="G46" s="40"/>
     </row>
-    <row r="47" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B47" s="73" t="s">
         <v>433</v>
       </c>
@@ -17635,7 +17635,7 @@
       <c r="E47" s="67"/>
       <c r="G47" s="40"/>
     </row>
-    <row r="48" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B48" s="73" t="s">
         <v>479</v>
       </c>
@@ -17649,7 +17649,7 @@
       <c r="E48" s="67"/>
       <c r="G48" s="40"/>
     </row>
-    <row r="49" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B49" s="73" t="s">
         <v>459</v>
       </c>
@@ -17663,7 +17663,7 @@
       <c r="E49" s="67"/>
       <c r="G49" s="40"/>
     </row>
-    <row r="50" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B50" s="73" t="s">
         <v>480</v>
       </c>
@@ -17677,7 +17677,7 @@
       <c r="E50" s="67"/>
       <c r="G50" s="40"/>
     </row>
-    <row r="51" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B51" s="73" t="s">
         <v>428</v>
       </c>
@@ -17691,7 +17691,7 @@
       <c r="E51" s="67"/>
       <c r="G51" s="40"/>
     </row>
-    <row r="52" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B52" s="73" t="s">
         <v>485</v>
       </c>
@@ -17705,7 +17705,7 @@
       <c r="E52" s="67"/>
       <c r="G52" s="40"/>
     </row>
-    <row r="53" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B53" s="73" t="s">
         <v>460</v>
       </c>
@@ -17719,7 +17719,7 @@
       <c r="E53" s="67"/>
       <c r="G53" s="40"/>
     </row>
-    <row r="54" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B54" s="73" t="s">
         <v>486</v>
       </c>
@@ -17733,7 +17733,7 @@
       <c r="E54" s="67"/>
       <c r="G54" s="40"/>
     </row>
-    <row r="55" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B55" s="73" t="s">
         <v>491</v>
       </c>
@@ -17747,7 +17747,7 @@
       <c r="E55" s="67"/>
       <c r="G55" s="40"/>
     </row>
-    <row r="56" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B56" s="73" t="s">
         <v>461</v>
       </c>
@@ -17761,7 +17761,7 @@
       <c r="E56" s="67"/>
       <c r="G56" s="40"/>
     </row>
-    <row r="57" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B57" s="73" t="s">
         <v>462</v>
       </c>
@@ -17775,7 +17775,7 @@
       <c r="E57" s="67"/>
       <c r="G57" s="40"/>
     </row>
-    <row r="58" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B58" s="73" t="s">
         <v>410</v>
       </c>
@@ -17789,7 +17789,7 @@
       <c r="E58" s="67"/>
       <c r="G58" s="40"/>
     </row>
-    <row r="59" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B59" s="73" t="s">
         <v>463</v>
       </c>
@@ -17803,7 +17803,7 @@
       <c r="E59" s="67"/>
       <c r="G59" s="40"/>
     </row>
-    <row r="60" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B60" s="73" t="s">
         <v>492</v>
       </c>
@@ -17817,7 +17817,7 @@
       <c r="E60" s="69"/>
       <c r="G60" s="40"/>
     </row>
-    <row r="61" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B61" s="73" t="s">
         <v>429</v>
       </c>
@@ -17831,7 +17831,7 @@
       <c r="E61" s="69"/>
       <c r="G61" s="40"/>
     </row>
-    <row r="62" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B62" s="73" t="s">
         <v>464</v>
       </c>
@@ -17845,7 +17845,7 @@
       <c r="E62" s="69"/>
       <c r="G62" s="40"/>
     </row>
-    <row r="63" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B63" s="73" t="s">
         <v>430</v>
       </c>
@@ -17859,7 +17859,7 @@
       <c r="E63" s="69"/>
       <c r="G63" s="40"/>
     </row>
-    <row r="64" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B64" s="73" t="s">
         <v>487</v>
       </c>
@@ -17873,7 +17873,7 @@
       <c r="E64" s="69"/>
       <c r="G64" s="40"/>
     </row>
-    <row r="65" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B65" s="73" t="s">
         <v>416</v>
       </c>
@@ -17887,7 +17887,7 @@
       <c r="E65" s="69"/>
       <c r="G65" s="40"/>
     </row>
-    <row r="66" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B66" s="73" t="s">
         <v>411</v>
       </c>
@@ -17901,7 +17901,7 @@
       <c r="E66" s="69"/>
       <c r="G66" s="40"/>
     </row>
-    <row r="67" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B67" s="73" t="s">
         <v>465</v>
       </c>
@@ -17915,7 +17915,7 @@
       <c r="E67" s="69"/>
       <c r="G67" s="40"/>
     </row>
-    <row r="68" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B68" s="73" t="s">
         <v>466</v>
       </c>
@@ -17929,7 +17929,7 @@
       <c r="E68" s="69"/>
       <c r="G68" s="40"/>
     </row>
-    <row r="69" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B69" s="73" t="s">
         <v>467</v>
       </c>
@@ -17943,7 +17943,7 @@
       <c r="E69" s="67"/>
       <c r="G69" s="40"/>
     </row>
-    <row r="70" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B70" s="73" t="s">
         <v>468</v>
       </c>
@@ -17957,7 +17957,7 @@
       <c r="E70" s="67"/>
       <c r="G70" s="40"/>
     </row>
-    <row r="71" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B71" s="73" t="s">
         <v>469</v>
       </c>
@@ -17971,7 +17971,7 @@
       <c r="E71" s="67"/>
       <c r="G71" s="40"/>
     </row>
-    <row r="72" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B72" s="73" t="s">
         <v>418</v>
       </c>
@@ -17985,7 +17985,7 @@
       <c r="E72" s="67"/>
       <c r="G72" s="40"/>
     </row>
-    <row r="73" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B73" s="73" t="s">
         <v>470</v>
       </c>
@@ -17999,7 +17999,7 @@
       <c r="E73" s="67"/>
       <c r="G73" s="40"/>
     </row>
-    <row r="74" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B74" s="73" t="s">
         <v>425</v>
       </c>
@@ -18013,7 +18013,7 @@
       <c r="E74" s="70"/>
       <c r="G74" s="40"/>
     </row>
-    <row r="75" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B75" s="73" t="s">
         <v>426</v>
       </c>
@@ -18027,7 +18027,7 @@
       <c r="E75" s="67"/>
       <c r="G75" s="40"/>
     </row>
-    <row r="76" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B76" s="73" t="s">
         <v>412</v>
       </c>
@@ -18041,7 +18041,7 @@
       <c r="E76" s="67"/>
       <c r="G76" s="40"/>
     </row>
-    <row r="77" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B77" s="73" t="s">
         <v>471</v>
       </c>
@@ -18055,7 +18055,7 @@
       <c r="E77" s="67"/>
       <c r="G77" s="40"/>
     </row>
-    <row r="78" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B78" s="73" t="s">
         <v>405</v>
       </c>
@@ -18069,7 +18069,7 @@
       <c r="E78" s="67"/>
       <c r="G78" s="40"/>
     </row>
-    <row r="79" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B79" s="73" t="s">
         <v>413</v>
       </c>
@@ -18082,7 +18082,7 @@
       </c>
       <c r="E79" s="67"/>
     </row>
-    <row r="80" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B80" s="73" t="s">
         <v>472</v>
       </c>
@@ -18095,7 +18095,7 @@
       </c>
       <c r="E80" s="67"/>
     </row>
-    <row r="81" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B81" s="73" t="s">
         <v>473</v>
       </c>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="E81" s="67"/>
     </row>
-    <row r="82" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B82" s="73" t="s">
         <v>474</v>
       </c>
@@ -18121,7 +18121,7 @@
       </c>
       <c r="E82" s="67"/>
     </row>
-    <row r="83" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B83" s="73" t="s">
         <v>475</v>
       </c>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="E83" s="67"/>
     </row>
-    <row r="84" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B84" s="73" t="s">
         <v>436</v>
       </c>
@@ -18147,7 +18147,7 @@
       </c>
       <c r="E84" s="67"/>
     </row>
-    <row r="85" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B85" s="73" t="s">
         <v>476</v>
       </c>
@@ -18160,7 +18160,7 @@
       </c>
       <c r="E85" s="67"/>
     </row>
-    <row r="86" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B86" s="73" t="s">
         <v>402</v>
       </c>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="E86" s="67"/>
     </row>
-    <row r="87" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B87" s="73" t="s">
         <v>427</v>
       </c>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="E87" s="67"/>
     </row>
-    <row r="88" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B88" s="73" t="s">
         <v>417</v>
       </c>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="E88" s="67"/>
     </row>
-    <row r="89" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B89" s="73" t="s">
         <v>423</v>
       </c>
@@ -18212,7 +18212,7 @@
       </c>
       <c r="E89" s="67"/>
     </row>
-    <row r="90" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B90" s="73" t="s">
         <v>424</v>
       </c>
@@ -18225,7 +18225,7 @@
       </c>
       <c r="E90" s="67"/>
     </row>
-    <row r="91" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B91" s="73" t="s">
         <v>477</v>
       </c>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="E91" s="67"/>
     </row>
-    <row r="92" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B92" s="73" t="s">
         <v>414</v>
       </c>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="E92" s="67"/>
     </row>
-    <row r="93" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B93" s="73" t="s">
         <v>415</v>
       </c>
@@ -18264,7 +18264,7 @@
       </c>
       <c r="E93" s="67"/>
     </row>
-    <row r="94" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B94" s="73" t="s">
         <v>489</v>
       </c>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="E94" s="67"/>
     </row>
-    <row r="95" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B95" s="73" t="s">
         <v>490</v>
       </c>
@@ -18290,7 +18290,7 @@
       </c>
       <c r="E95" s="67"/>
     </row>
-    <row r="96" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B96" s="74" t="s">
         <v>401</v>
       </c>
@@ -18328,16 +18328,16 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A2:G48"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="36.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="85.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="36.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="85.85546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
         <v>679</v>
       </c>
@@ -18345,14 +18345,14 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:7" s="7" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="1:7" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
         <v>8</v>
       </c>
@@ -18366,7 +18366,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="18" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="17.25" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B5" s="72" t="s">
         <v>72</v>
       </c>
@@ -18379,7 +18379,7 @@
       </c>
       <c r="E5" s="68"/>
     </row>
-    <row r="6" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B6" s="73" t="s">
         <v>27</v>
       </c>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="E6" s="67"/>
     </row>
-    <row r="7" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B7" s="73" t="s">
         <v>57</v>
       </c>
@@ -18405,7 +18405,7 @@
       </c>
       <c r="E7" s="67"/>
     </row>
-    <row r="8" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B8" s="73" t="s">
         <v>41</v>
       </c>
@@ -18418,7 +18418,7 @@
       </c>
       <c r="E8" s="67"/>
     </row>
-    <row r="9" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="73" t="s">
         <v>73</v>
       </c>
@@ -18431,7 +18431,7 @@
       </c>
       <c r="E9" s="67"/>
     </row>
-    <row r="10" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B10" s="73" t="s">
         <v>724</v>
       </c>
@@ -18444,7 +18444,7 @@
       </c>
       <c r="E10" s="67"/>
     </row>
-    <row r="11" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B11" s="73" t="s">
         <v>86</v>
       </c>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E11" s="67"/>
     </row>
-    <row r="12" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B12" s="73" t="s">
         <v>55</v>
       </c>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="E12" s="67"/>
     </row>
-    <row r="13" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B13" s="73" t="s">
         <v>59</v>
       </c>
@@ -18484,7 +18484,7 @@
       <c r="E13" s="67"/>
       <c r="G13" s="40"/>
     </row>
-    <row r="14" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B14" s="73" t="s">
         <v>725</v>
       </c>
@@ -18498,7 +18498,7 @@
       <c r="E14" s="67"/>
       <c r="G14" s="40"/>
     </row>
-    <row r="15" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B15" s="73" t="s">
         <v>36</v>
       </c>
@@ -18512,7 +18512,7 @@
       <c r="E15" s="67"/>
       <c r="G15" s="40"/>
     </row>
-    <row r="16" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="73" t="s">
         <v>39</v>
       </c>
@@ -18526,7 +18526,7 @@
       <c r="E16" s="67"/>
       <c r="G16" s="40"/>
     </row>
-    <row r="17" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B17" s="73" t="s">
         <v>726</v>
       </c>
@@ -18540,7 +18540,7 @@
       <c r="E17" s="67"/>
       <c r="G17" s="40"/>
     </row>
-    <row r="18" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B18" s="73" t="s">
         <v>75</v>
       </c>
@@ -18554,7 +18554,7 @@
       <c r="E18" s="67"/>
       <c r="G18" s="40"/>
     </row>
-    <row r="19" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="73" t="s">
         <v>43</v>
       </c>
@@ -18568,7 +18568,7 @@
       <c r="E19" s="67"/>
       <c r="G19" s="40"/>
     </row>
-    <row r="20" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B20" s="73" t="s">
         <v>60</v>
       </c>
@@ -18582,7 +18582,7 @@
       <c r="E20" s="67"/>
       <c r="G20" s="40"/>
     </row>
-    <row r="21" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B21" s="73" t="s">
         <v>727</v>
       </c>
@@ -18596,7 +18596,7 @@
       <c r="E21" s="67"/>
       <c r="G21" s="40"/>
     </row>
-    <row r="22" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B22" s="73" t="s">
         <v>64</v>
       </c>
@@ -18610,7 +18610,7 @@
       <c r="E22" s="67"/>
       <c r="G22" s="40"/>
     </row>
-    <row r="23" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B23" s="73" t="s">
         <v>728</v>
       </c>
@@ -18624,7 +18624,7 @@
       <c r="E23" s="67"/>
       <c r="G23" s="40"/>
     </row>
-    <row r="24" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B24" s="73" t="s">
         <v>77</v>
       </c>
@@ -18638,7 +18638,7 @@
       <c r="E24" s="67"/>
       <c r="G24" s="40"/>
     </row>
-    <row r="25" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B25" s="73" t="s">
         <v>729</v>
       </c>
@@ -18652,7 +18652,7 @@
       <c r="E25" s="67"/>
       <c r="G25" s="40"/>
     </row>
-    <row r="26" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B26" s="73" t="s">
         <v>730</v>
       </c>
@@ -18666,7 +18666,7 @@
       <c r="E26" s="67"/>
       <c r="G26" s="40"/>
     </row>
-    <row r="27" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B27" s="73" t="s">
         <v>731</v>
       </c>
@@ -18680,7 +18680,7 @@
       <c r="E27" s="67"/>
       <c r="G27" s="40"/>
     </row>
-    <row r="28" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B28" s="73" t="s">
         <v>732</v>
       </c>
@@ -18694,7 +18694,7 @@
       <c r="E28" s="67"/>
       <c r="G28" s="40"/>
     </row>
-    <row r="29" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B29" s="73" t="s">
         <v>733</v>
       </c>
@@ -18708,7 +18708,7 @@
       <c r="E29" s="67"/>
       <c r="G29" s="40"/>
     </row>
-    <row r="30" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B30" s="73" t="s">
         <v>15</v>
       </c>
@@ -18722,7 +18722,7 @@
       <c r="E30" s="67"/>
       <c r="G30" s="40"/>
     </row>
-    <row r="31" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B31" s="73" t="s">
         <v>734</v>
       </c>
@@ -18736,7 +18736,7 @@
       <c r="E31" s="67"/>
       <c r="G31" s="40"/>
     </row>
-    <row r="32" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B32" s="73" t="s">
         <v>735</v>
       </c>
@@ -18750,7 +18750,7 @@
       <c r="E32" s="67"/>
       <c r="G32" s="40"/>
     </row>
-    <row r="33" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B33" s="73" t="s">
         <v>74</v>
       </c>
@@ -18764,7 +18764,7 @@
       <c r="E33" s="67"/>
       <c r="G33" s="40"/>
     </row>
-    <row r="34" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B34" s="73" t="s">
         <v>736</v>
       </c>
@@ -18778,7 +18778,7 @@
       <c r="E34" s="67"/>
       <c r="G34" s="40"/>
     </row>
-    <row r="35" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B35" s="73" t="s">
         <v>737</v>
       </c>
@@ -18792,7 +18792,7 @@
       <c r="E35" s="67"/>
       <c r="G35" s="40"/>
     </row>
-    <row r="36" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B36" s="73" t="s">
         <v>738</v>
       </c>
@@ -18806,7 +18806,7 @@
       <c r="E36" s="67"/>
       <c r="G36" s="40"/>
     </row>
-    <row r="37" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B37" s="73" t="s">
         <v>21</v>
       </c>
@@ -18820,7 +18820,7 @@
       <c r="E37" s="67"/>
       <c r="G37" s="40"/>
     </row>
-    <row r="38" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B38" s="73" t="s">
         <v>739</v>
       </c>
@@ -18834,7 +18834,7 @@
       <c r="E38" s="67"/>
       <c r="G38" s="40"/>
     </row>
-    <row r="39" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B39" s="73" t="s">
         <v>740</v>
       </c>
@@ -18848,7 +18848,7 @@
       <c r="E39" s="67"/>
       <c r="G39" s="40"/>
     </row>
-    <row r="40" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B40" s="73" t="s">
         <v>87</v>
       </c>
@@ -18862,7 +18862,7 @@
       <c r="E40" s="67"/>
       <c r="G40" s="40"/>
     </row>
-    <row r="41" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B41" s="73" t="s">
         <v>42</v>
       </c>
@@ -18876,7 +18876,7 @@
       <c r="E41" s="67"/>
       <c r="G41" s="40"/>
     </row>
-    <row r="42" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B42" s="73" t="s">
         <v>741</v>
       </c>
@@ -18890,7 +18890,7 @@
       <c r="E42" s="67"/>
       <c r="G42" s="40"/>
     </row>
-    <row r="43" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B43" s="73" t="s">
         <v>68</v>
       </c>
@@ -18904,7 +18904,7 @@
       <c r="E43" s="67"/>
       <c r="G43" s="40"/>
     </row>
-    <row r="44" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B44" s="73" t="s">
         <v>742</v>
       </c>
@@ -18918,7 +18918,7 @@
       <c r="E44" s="67"/>
       <c r="G44" s="40"/>
     </row>
-    <row r="45" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B45" s="73" t="s">
         <v>743</v>
       </c>
@@ -18932,7 +18932,7 @@
       <c r="E45" s="67"/>
       <c r="G45" s="40"/>
     </row>
-    <row r="46" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B46" s="73" t="s">
         <v>744</v>
       </c>
@@ -18946,7 +18946,7 @@
       <c r="E46" s="67"/>
       <c r="G46" s="40"/>
     </row>
-    <row r="47" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B47" s="73" t="s">
         <v>745</v>
       </c>
@@ -18960,7 +18960,7 @@
       <c r="E47" s="67"/>
       <c r="G47" s="40"/>
     </row>
-    <row r="48" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B48" s="73" t="s">
         <v>38</v>
       </c>
@@ -18991,25 +18991,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="7084a2b3-cb11-4906-a43c-1a4adb60eb1a">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b70e718c-23eb-44d0-9a91-64212c881416">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7084a2b3-cb11-4906-a43c-1a4adb60eb1a" xsi:nil="true"/>
-    <_xbe44__xace0_ xmlns="b70e718c-23eb-44d0-9a91-64212c881416" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010057045470FDD61748887FE91473DB7B8A" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="801b26fdcf284eceb351ce719e8bf508">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b70e718c-23eb-44d0-9a91-64212c881416" xmlns:ns3="7084a2b3-cb11-4906-a43c-1a4adb60eb1a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e6e85c3fec1035b83d6823589f5d557a" ns2:_="" ns3:_="">
     <xsd:import namespace="b70e718c-23eb-44d0-9a91-64212c881416"/>
@@ -19246,6 +19227,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="7084a2b3-cb11-4906-a43c-1a4adb60eb1a">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b70e718c-23eb-44d0-9a91-64212c881416">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7084a2b3-cb11-4906-a43c-1a4adb60eb1a" xsi:nil="true"/>
+    <_xbe44__xace0_ xmlns="b70e718c-23eb-44d0-9a91-64212c881416" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F86E0441-11BE-4F64-971D-6310BC063B83}">
   <ds:schemaRefs>
@@ -19255,23 +19255,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E453FEC-FA85-4073-8FF1-1D077117D35D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="b70e718c-23eb-44d0-9a91-64212c881416"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7084a2b3-cb11-4906-a43c-1a4adb60eb1a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70C3E720-EB61-42B0-A0F2-B2B3E96F1D58}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19288,4 +19271,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E453FEC-FA85-4073-8FF1-1D077117D35D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="b70e718c-23eb-44d0-9a91-64212c881416"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7084a2b3-cb11-4906-a43c-1a4adb60eb1a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>